--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>(0/0)</t>
+  </si>
+  <si>
+    <t>Testlauf 1 - 2026-09-18 21:23:05</t>
   </si>
 </sst>
 </file>
@@ -255,7 +258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -639,6 +642,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="0">
+        <v>0.42</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0.23</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="0">
+        <v>0.23</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="0">
+        <v>1</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="0">
+        <v>1</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="0">
+        <v>1</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="0">
+        <v>1</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="0">
+        <v>1</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.96</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="0">
+        <v>0.02</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I29" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="0">
+        <v>0</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="0">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" s="0">
+        <v>0</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="0">
+        <v>0</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -213,6 +213,78 @@
   </si>
   <si>
     <t>Testlauf 1 - 2026-09-18 21:23:05</t>
+  </si>
+  <si>
+    <t>Testlauf 3 - 2026-09-21 06:49:47</t>
+  </si>
+  <si>
+    <t>(309/446)</t>
+  </si>
+  <si>
+    <t>(1459/2708)</t>
+  </si>
+  <si>
+    <t>(5705/12043)</t>
+  </si>
+  <si>
+    <t>(2655/6046)</t>
+  </si>
+  <si>
+    <t>(7/7)</t>
+  </si>
+  <si>
+    <t>(26/28)</t>
+  </si>
+  <si>
+    <t>(87/103)</t>
+  </si>
+  <si>
+    <t>(43/56)</t>
+  </si>
+  <si>
+    <t>(102/199)</t>
+  </si>
+  <si>
+    <t>(346/1182)</t>
+  </si>
+  <si>
+    <t>(1528/5242)</t>
+  </si>
+  <si>
+    <t>(624/2004)</t>
+  </si>
+  <si>
+    <t>(137/160)</t>
+  </si>
+  <si>
+    <t>(624/861)</t>
+  </si>
+  <si>
+    <t>(2382/4190)</t>
+  </si>
+  <si>
+    <t>(1191/2483)</t>
+  </si>
+  <si>
+    <t>(30/31)</t>
+  </si>
+  <si>
+    <t>(219/258)</t>
+  </si>
+  <si>
+    <t>(864/1094)</t>
+  </si>
+  <si>
+    <t>(432/733)</t>
+  </si>
+  <si>
+    <t>(26/63)</t>
+  </si>
+  <si>
+    <t>(78/156)</t>
+  </si>
+  <si>
+    <t>(4/66)</t>
   </si>
 </sst>
 </file>
@@ -258,7 +330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -1012,6 +1084,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="0">
+        <v>1</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H38" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I38" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="0">
+        <v>1</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H40" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J40" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="I41" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="0">
+        <v>1</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="0">
+        <v>1</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="0">
+        <v>1</v>
+      </c>
+      <c r="H42" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G43" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H43" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="I44" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E45" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I45" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J45" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H46" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I46" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H47" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I47" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="J47" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="0">
+        <v>0</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="0">
+        <v>0</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="0">
+        <v>0</v>
+      </c>
+      <c r="H48" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I48" s="0">
+        <v>0</v>
+      </c>
+      <c r="J48" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -285,6 +285,12 @@
   </si>
   <si>
     <t>(4/66)</t>
+  </si>
+  <si>
+    <t>Testlauf 4 - 2026-09-21 20:00:31</t>
+  </si>
+  <si>
+    <t>Testlauf 5 - 2026-09-21 20:35:46</t>
   </si>
 </sst>
 </file>
@@ -330,7 +336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -1454,6 +1460,746 @@
         <v>65</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I53" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="I54" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="0">
+        <v>1</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I55" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G56" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H56" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I56" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="0">
+        <v>1</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="0">
+        <v>1</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H57" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="E58" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="G58" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="I58" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="0">
+        <v>1</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" s="0">
+        <v>1</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" s="0">
+        <v>1</v>
+      </c>
+      <c r="H59" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I59" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H60" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I60" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H61" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="I61" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J61" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G62" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I62" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C63" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E63" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G63" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H63" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I63" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J63" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E64" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G64" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H64" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I64" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="J64" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="0">
+        <v>0</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E65" s="0">
+        <v>0</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G65" s="0">
+        <v>0</v>
+      </c>
+      <c r="H65" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I65" s="0">
+        <v>0</v>
+      </c>
+      <c r="J65" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I70" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E71" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F71" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="G71" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="H71" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="I71" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J71" s="0" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="0">
+        <v>1</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E72" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F72" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G72" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H72" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I72" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J72" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H73" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I73" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J73" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="0">
+        <v>1</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" s="0">
+        <v>1</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H74" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J74" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H75" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="I75" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J75" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="0">
+        <v>1</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E76" s="0">
+        <v>1</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" s="0">
+        <v>1</v>
+      </c>
+      <c r="H76" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I76" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J76" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C77" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G77" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H77" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I77" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J77" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E78" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G78" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H78" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="I78" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E79" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G79" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H79" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I79" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E80" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G80" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H80" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I80" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J80" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E81" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G81" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I81" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="J81" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="0">
+        <v>0</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E82" s="0">
+        <v>0</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G82" s="0">
+        <v>0</v>
+      </c>
+      <c r="H82" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I82" s="0">
+        <v>0</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -291,6 +291,36 @@
   </si>
   <si>
     <t>Testlauf 5 - 2026-09-21 20:35:46</t>
+  </si>
+  <si>
+    <t>Testlauf 6 - 2026-09-21 20:49:56</t>
+  </si>
+  <si>
+    <t>(311/448)</t>
+  </si>
+  <si>
+    <t>(1478/2727)</t>
+  </si>
+  <si>
+    <t>(5744/12088)</t>
+  </si>
+  <si>
+    <t>(2685/6074)</t>
+  </si>
+  <si>
+    <t>(139/162)</t>
+  </si>
+  <si>
+    <t>(643/880)</t>
+  </si>
+  <si>
+    <t>(2421/4235)</t>
+  </si>
+  <si>
+    <t>(1220/2511)</t>
+  </si>
+  <si>
+    <t>(103/282)</t>
   </si>
 </sst>
 </file>
@@ -336,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -2200,6 +2230,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I87" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D88" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="E88" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G88" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="H88" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="I88" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J88" s="0" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="0">
+        <v>1</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E89" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G89" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H89" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I89" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E90" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F90" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G90" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H90" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I90" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J90" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="0">
+        <v>1</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="0">
+        <v>1</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H91" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J91" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E92" s="0">
+        <v>0.73</v>
+      </c>
+      <c r="F92" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="G92" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H92" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="I92" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="J92" s="0" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="0">
+        <v>1</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E93" s="0">
+        <v>1</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" s="0">
+        <v>1</v>
+      </c>
+      <c r="H93" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I93" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J93" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G94" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H94" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I94" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J94" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C95" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D95" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E95" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F95" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G95" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H95" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="I95" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J95" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E96" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F96" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G96" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H96" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I96" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C97" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D97" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E97" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F97" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G97" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H97" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I97" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J97" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C98" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D98" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E98" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F98" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G98" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H98" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I98" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J98" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C99" s="0">
+        <v>0</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E99" s="0">
+        <v>0</v>
+      </c>
+      <c r="F99" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G99" s="0">
+        <v>0</v>
+      </c>
+      <c r="H99" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I99" s="0">
+        <v>0</v>
+      </c>
+      <c r="J99" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -321,6 +321,18 @@
   </si>
   <si>
     <t>(103/282)</t>
+  </si>
+  <si>
+    <t>Testlauf 7 - 2026-09-21 21:22:16</t>
+  </si>
+  <si>
+    <t>(2687/6074)</t>
+  </si>
+  <si>
+    <t>(625/2004)</t>
+  </si>
+  <si>
+    <t>(1221/2511)</t>
   </si>
 </sst>
 </file>
@@ -366,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -2600,6 +2612,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I104" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D105" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="E105" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F105" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G105" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="H105" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="I105" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J105" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" s="0">
+        <v>1</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E106" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G106" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H106" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I106" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J106" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D107" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E107" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F107" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G107" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H107" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="I107" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J107" s="0" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="0">
+        <v>1</v>
+      </c>
+      <c r="D108" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E108" s="0">
+        <v>1</v>
+      </c>
+      <c r="F108" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H108" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J108" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" s="0">
+        <v>0.73</v>
+      </c>
+      <c r="F109" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="G109" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H109" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="I109" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="J109" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="0">
+        <v>1</v>
+      </c>
+      <c r="D110" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E110" s="0">
+        <v>1</v>
+      </c>
+      <c r="F110" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" s="0">
+        <v>1</v>
+      </c>
+      <c r="H110" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I110" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J110" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D111" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F111" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G111" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H111" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I111" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J111" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C112" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E112" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F112" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="G112" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H112" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="I112" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J112" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C113" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D113" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E113" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F113" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G113" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H113" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I113" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J113" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C114" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E114" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F114" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G114" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H114" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I114" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J114" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E115" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F115" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G115" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H115" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I115" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J115" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" s="0">
+        <v>0</v>
+      </c>
+      <c r="D116" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E116" s="0">
+        <v>0</v>
+      </c>
+      <c r="F116" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G116" s="0">
+        <v>0</v>
+      </c>
+      <c r="H116" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I116" s="0">
+        <v>0</v>
+      </c>
+      <c r="J116" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -333,6 +333,66 @@
   </si>
   <si>
     <t>(1221/2511)</t>
+  </si>
+  <si>
+    <t>Testlauf 8 - 2026-09-22 11:12:21</t>
+  </si>
+  <si>
+    <t>(1469/2727)</t>
+  </si>
+  <si>
+    <t>(5703/12088)</t>
+  </si>
+  <si>
+    <t>(2658/6074)</t>
+  </si>
+  <si>
+    <t>(1524/5242)</t>
+  </si>
+  <si>
+    <t>(618/2004)</t>
+  </si>
+  <si>
+    <t>(2415/4235)</t>
+  </si>
+  <si>
+    <t>(1218/2511)</t>
+  </si>
+  <si>
+    <t>(89/125)</t>
+  </si>
+  <si>
+    <t>(317/475)</t>
+  </si>
+  <si>
+    <t>(141/260)</t>
+  </si>
+  <si>
+    <t>(221/258)</t>
+  </si>
+  <si>
+    <t>(875/1094)</t>
+  </si>
+  <si>
+    <t>(441/733)</t>
+  </si>
+  <si>
+    <t>Testlauf 9 - 2026-09-22 13:41:55</t>
+  </si>
+  <si>
+    <t>(1480/2727)</t>
+  </si>
+  <si>
+    <t>(5749/12088)</t>
+  </si>
+  <si>
+    <t>(619/2004)</t>
+  </si>
+  <si>
+    <t>(2419/4235)</t>
+  </si>
+  <si>
+    <t>(166/260)</t>
   </si>
 </sst>
 </file>
@@ -378,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -2982,6 +3042,746 @@
         <v>65</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G121" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I121" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="E122" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F122" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="G122" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="H122" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="I122" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J122" s="0" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="0">
+        <v>1</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E123" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F123" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G123" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H123" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I123" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J123" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E124" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F124" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G124" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H124" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="I124" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J124" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="0">
+        <v>1</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E125" s="0">
+        <v>1</v>
+      </c>
+      <c r="F125" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H125" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J125" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E126" s="0">
+        <v>0.73</v>
+      </c>
+      <c r="F126" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="G126" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H126" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="I126" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="J126" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" s="0">
+        <v>1</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E127" s="0">
+        <v>1</v>
+      </c>
+      <c r="F127" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" s="0">
+        <v>1</v>
+      </c>
+      <c r="H127" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J127" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C128" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E128" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="F128" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="G128" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="H128" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="I128" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="J128" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C129" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E129" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F129" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="G129" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="H129" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="I129" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="J129" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C130" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E130" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F130" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G130" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H130" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I130" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J130" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C131" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E131" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F131" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G131" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H131" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I131" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J131" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C132" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E132" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F132" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G132" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H132" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I132" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J132" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C133" s="0">
+        <v>0</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E133" s="0">
+        <v>0</v>
+      </c>
+      <c r="F133" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G133" s="0">
+        <v>0</v>
+      </c>
+      <c r="H133" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I133" s="0">
+        <v>0</v>
+      </c>
+      <c r="J133" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G138" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I138" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="E139" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="G139" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="H139" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="I139" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J139" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="0">
+        <v>1</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E140" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G140" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H140" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I140" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J140" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="E141" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="G141" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H141" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="I141" s="0">
+        <v>0.31</v>
+      </c>
+      <c r="J141" s="0" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C142" s="0">
+        <v>1</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142" s="0">
+        <v>1</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H142" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I142" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J142" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E143" s="0">
+        <v>0.73</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="G143" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H143" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="I143" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="J143" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="0">
+        <v>1</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E144" s="0">
+        <v>1</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G144" s="0">
+        <v>1</v>
+      </c>
+      <c r="H144" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I144" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J144" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C145" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E145" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F145" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G145" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H145" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I145" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J145" s="0" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E146" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="G146" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="H146" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="I146" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="J146" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C147" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E147" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G147" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H147" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I147" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J147" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C148" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E148" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G148" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H148" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I148" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J148" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C149" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E149" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G149" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H149" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I149" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J149" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C150" s="0">
+        <v>0</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E150" s="0">
+        <v>0</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G150" s="0">
+        <v>0</v>
+      </c>
+      <c r="H150" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I150" s="0">
+        <v>0</v>
+      </c>
+      <c r="J150" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -393,6 +393,45 @@
   </si>
   <si>
     <t>(166/260)</t>
+  </si>
+  <si>
+    <t>Testlauf 10 - 2026-09-23 15:45:39</t>
+  </si>
+  <si>
+    <t>(313/451)</t>
+  </si>
+  <si>
+    <t>(1489/2774)</t>
+  </si>
+  <si>
+    <t>(5817/12394)</t>
+  </si>
+  <si>
+    <t>(2706/6190)</t>
+  </si>
+  <si>
+    <t>(104/202)</t>
+  </si>
+  <si>
+    <t>(354/1228)</t>
+  </si>
+  <si>
+    <t>(1580/5531)</t>
+  </si>
+  <si>
+    <t>(632/2110)</t>
+  </si>
+  <si>
+    <t>(101/126)</t>
+  </si>
+  <si>
+    <t>(369/492)</t>
+  </si>
+  <si>
+    <t>(172/270)</t>
+  </si>
+  <si>
+    <t>(877/1094)</t>
   </si>
 </sst>
 </file>
@@ -438,10 +477,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
+    <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="10.1179599761963" customWidth="1"/>
     <col min="5" max="5" width="11.0295114517212" customWidth="1"/>
@@ -3782,6 +3821,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="0" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G155" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I155" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="0">
+        <v>0.69</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="E156" s="0">
+        <v>0.54</v>
+      </c>
+      <c r="F156" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="G156" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="H156" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="I156" s="0">
+        <v>0.44</v>
+      </c>
+      <c r="J156" s="0" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="0">
+        <v>1</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E157" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F157" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G157" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H157" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I157" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J157" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="E158" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="F158" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="G158" s="0">
+        <v>0.29</v>
+      </c>
+      <c r="H158" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="I158" s="0">
+        <v>0.3</v>
+      </c>
+      <c r="J158" s="0" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C159" s="0">
+        <v>1</v>
+      </c>
+      <c r="D159" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" s="0">
+        <v>1</v>
+      </c>
+      <c r="F159" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G159" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H159" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J159" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D160" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E160" s="0">
+        <v>0.73</v>
+      </c>
+      <c r="F160" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="G160" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H160" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="I160" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="J160" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161" s="0">
+        <v>1</v>
+      </c>
+      <c r="D161" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E161" s="0">
+        <v>1</v>
+      </c>
+      <c r="F161" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G161" s="0">
+        <v>1</v>
+      </c>
+      <c r="H161" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J161" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C162" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D162" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E162" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F162" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="G162" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H162" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="I162" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J162" s="0" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C163" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D163" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E163" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F163" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="G163" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="H163" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="I163" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="J163" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C164" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D164" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E164" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="F164" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="G164" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H164" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="I164" s="0">
+        <v>0.06</v>
+      </c>
+      <c r="J164" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C165" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D165" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E165" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F165" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G165" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H165" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I165" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J165" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C166" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="D166" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E166" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F166" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G166" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="H166" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="I166" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J166" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C167" s="0">
+        <v>0</v>
+      </c>
+      <c r="D167" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E167" s="0">
+        <v>0</v>
+      </c>
+      <c r="F167" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G167" s="0">
+        <v>0</v>
+      </c>
+      <c r="H167" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I167" s="0">
+        <v>0</v>
+      </c>
+      <c r="J167" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -333,6 +333,78 @@
   </si>
   <si>
     <t>(1221/2511)</t>
+  </si>
+  <si>
+    <t>Testlauf 8 - 2026-09-24 19:04:58</t>
+  </si>
+  <si>
+    <t>(338/448)</t>
+  </si>
+  <si>
+    <t>(1633/2727)</t>
+  </si>
+  <si>
+    <t>(6464/12088)</t>
+  </si>
+  <si>
+    <t>(2932/6074)</t>
+  </si>
+  <si>
+    <t>(123/199)</t>
+  </si>
+  <si>
+    <t>(422/1182)</t>
+  </si>
+  <si>
+    <t>(2037/5242)</t>
+  </si>
+  <si>
+    <t>(734/2004)</t>
+  </si>
+  <si>
+    <t>(647/880)</t>
+  </si>
+  <si>
+    <t>(2452/4235)</t>
+  </si>
+  <si>
+    <t>(1259/2511)</t>
+  </si>
+  <si>
+    <t>(170/260)</t>
+  </si>
+  <si>
+    <t>(221/258)</t>
+  </si>
+  <si>
+    <t>(866/1094)</t>
+  </si>
+  <si>
+    <t>(434/733)</t>
+  </si>
+  <si>
+    <t>(63/63)</t>
+  </si>
+  <si>
+    <t>(156/156)</t>
+  </si>
+  <si>
+    <t>(47/66)</t>
+  </si>
+  <si>
+    <t>(14/16)</t>
+  </si>
+  <si>
+    <t>(87/101)</t>
+  </si>
+  <si>
+    <t>(288/405)</t>
+  </si>
+  <si>
+    <t>(155/282)</t>
+  </si>
+  <si>
+    <t>Testlauf 9 - 2026-09-24 19:26:08</t>
   </si>
 </sst>
 </file>
@@ -378,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
@@ -2982,6 +3054,746 @@
         <v>65</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="0" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G121" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I121" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="D122" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="E122" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="F122" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="G122" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="H122" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="I122" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J122" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="0">
+        <v>1</v>
+      </c>
+      <c r="D123" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E123" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F123" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G123" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H123" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I123" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J123" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="E124" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="F124" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="G124" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H124" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="I124" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J124" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" s="0">
+        <v>1</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E125" s="0">
+        <v>1</v>
+      </c>
+      <c r="F125" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H125" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J125" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E126" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="F126" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="G126" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="H126" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="I126" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J126" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" s="0">
+        <v>1</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E127" s="0">
+        <v>1</v>
+      </c>
+      <c r="F127" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" s="0">
+        <v>1</v>
+      </c>
+      <c r="H127" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J127" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C128" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E128" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F128" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G128" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H128" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I128" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J128" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C129" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D129" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E129" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F129" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="G129" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H129" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="I129" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J129" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C130" s="0">
+        <v>1</v>
+      </c>
+      <c r="D130" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E130" s="0">
+        <v>1</v>
+      </c>
+      <c r="F130" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G130" s="0">
+        <v>1</v>
+      </c>
+      <c r="H130" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I130" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J130" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C131" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D131" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E131" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F131" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G131" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H131" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I131" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J131" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C132" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D132" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E132" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F132" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="G132" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H132" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="I132" s="0">
+        <v>0.55</v>
+      </c>
+      <c r="J132" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C133" s="0">
+        <v>0</v>
+      </c>
+      <c r="D133" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E133" s="0">
+        <v>0</v>
+      </c>
+      <c r="F133" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G133" s="0">
+        <v>0</v>
+      </c>
+      <c r="H133" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I133" s="0">
+        <v>0</v>
+      </c>
+      <c r="J133" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G138" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I138" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="E139" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="F139" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="G139" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="H139" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="I139" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J139" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="0">
+        <v>1</v>
+      </c>
+      <c r="D140" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E140" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F140" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G140" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H140" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I140" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J140" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D141" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="E141" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="F141" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="G141" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H141" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="I141" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J141" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C142" s="0">
+        <v>1</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142" s="0">
+        <v>1</v>
+      </c>
+      <c r="F142" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H142" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I142" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J142" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D143" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E143" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="F143" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="G143" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="H143" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="I143" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J143" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="0">
+        <v>1</v>
+      </c>
+      <c r="D144" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E144" s="0">
+        <v>1</v>
+      </c>
+      <c r="F144" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G144" s="0">
+        <v>1</v>
+      </c>
+      <c r="H144" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I144" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J144" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C145" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D145" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E145" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F145" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G145" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H145" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I145" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J145" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D146" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E146" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F146" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="G146" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H146" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="I146" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J146" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C147" s="0">
+        <v>1</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E147" s="0">
+        <v>1</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G147" s="0">
+        <v>1</v>
+      </c>
+      <c r="H147" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I147" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J147" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C148" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D148" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E148" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F148" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G148" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H148" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I148" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J148" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C149" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E149" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F149" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="G149" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H149" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="I149" s="0">
+        <v>0.55</v>
+      </c>
+      <c r="J149" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C150" s="0">
+        <v>0</v>
+      </c>
+      <c r="D150" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E150" s="0">
+        <v>0</v>
+      </c>
+      <c r="F150" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G150" s="0">
+        <v>0</v>
+      </c>
+      <c r="H150" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I150" s="0">
+        <v>0</v>
+      </c>
+      <c r="J150" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -405,6 +405,42 @@
   </si>
   <si>
     <t>Testlauf 9 - 2026-09-24 19:26:08</t>
+  </si>
+  <si>
+    <t>Testlauf 10 - 2026-09-24 19:39:40</t>
+  </si>
+  <si>
+    <t>(340/451)</t>
+  </si>
+  <si>
+    <t>(1642/2774)</t>
+  </si>
+  <si>
+    <t>(6532/12394)</t>
+  </si>
+  <si>
+    <t>(2953/6190)</t>
+  </si>
+  <si>
+    <t>(125/202)</t>
+  </si>
+  <si>
+    <t>(430/1228)</t>
+  </si>
+  <si>
+    <t>(2095/5531)</t>
+  </si>
+  <si>
+    <t>(749/2110)</t>
+  </si>
+  <si>
+    <t>(101/126)</t>
+  </si>
+  <si>
+    <t>(369/492)</t>
+  </si>
+  <si>
+    <t>(176/270)</t>
   </si>
 </sst>
 </file>
@@ -450,10 +486,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.9204120635986" customWidth="1"/>
+    <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="10.1179599761963" customWidth="1"/>
     <col min="5" max="5" width="11.0295114517212" customWidth="1"/>
@@ -3794,6 +3830,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="0" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G155" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I155" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="D156" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="E156" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="F156" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="G156" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="H156" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="I156" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J156" s="0" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="0">
+        <v>1</v>
+      </c>
+      <c r="D157" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E157" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F157" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G157" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H157" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I157" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J157" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D158" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="E158" s="0">
+        <v>0.35</v>
+      </c>
+      <c r="F158" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="G158" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="H158" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="I158" s="0">
+        <v>0.35</v>
+      </c>
+      <c r="J158" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C159" s="0">
+        <v>1</v>
+      </c>
+      <c r="D159" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" s="0">
+        <v>1</v>
+      </c>
+      <c r="F159" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G159" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H159" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J159" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D160" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E160" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="F160" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="G160" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="H160" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="I160" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J160" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161" s="0">
+        <v>1</v>
+      </c>
+      <c r="D161" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E161" s="0">
+        <v>1</v>
+      </c>
+      <c r="F161" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G161" s="0">
+        <v>1</v>
+      </c>
+      <c r="H161" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J161" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C162" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D162" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E162" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F162" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="G162" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H162" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="I162" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J162" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C163" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D163" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E163" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F163" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="G163" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H163" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="I163" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J163" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C164" s="0">
+        <v>1</v>
+      </c>
+      <c r="D164" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E164" s="0">
+        <v>1</v>
+      </c>
+      <c r="F164" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G164" s="0">
+        <v>1</v>
+      </c>
+      <c r="H164" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I164" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J164" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C165" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D165" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E165" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F165" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G165" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H165" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I165" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J165" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C166" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D166" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E166" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F166" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="G166" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H166" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="I166" s="0">
+        <v>0.55</v>
+      </c>
+      <c r="J166" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C167" s="0">
+        <v>0</v>
+      </c>
+      <c r="D167" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E167" s="0">
+        <v>0</v>
+      </c>
+      <c r="F167" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G167" s="0">
+        <v>0</v>
+      </c>
+      <c r="H167" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I167" s="0">
+        <v>0</v>
+      </c>
+      <c r="J167" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>(176/270)</t>
+  </si>
+  <si>
+    <t>Testlauf 11 - 2026-09-26 21:55:45</t>
   </si>
 </sst>
 </file>
@@ -486,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -4200,6 +4203,376 @@
         <v>65</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="0" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C172" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E172" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G172" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I172" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="D173" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="E173" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="F173" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="G173" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="H173" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="I173" s="0">
+        <v>0.48</v>
+      </c>
+      <c r="J173" s="0" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="0">
+        <v>1</v>
+      </c>
+      <c r="D174" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E174" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F174" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G174" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H174" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I174" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J174" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D175" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="E175" s="0">
+        <v>0.35</v>
+      </c>
+      <c r="F175" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="G175" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="H175" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="I175" s="0">
+        <v>0.35</v>
+      </c>
+      <c r="J175" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C176" s="0">
+        <v>1</v>
+      </c>
+      <c r="D176" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E176" s="0">
+        <v>1</v>
+      </c>
+      <c r="F176" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G176" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H176" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I176" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J176" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="D177" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="E177" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="F177" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="G177" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="H177" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="I177" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J177" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="0">
+        <v>1</v>
+      </c>
+      <c r="D178" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E178" s="0">
+        <v>1</v>
+      </c>
+      <c r="F178" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G178" s="0">
+        <v>1</v>
+      </c>
+      <c r="H178" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I178" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J178" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C179" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D179" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E179" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="F179" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="G179" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H179" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="I179" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="J179" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C180" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D180" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E180" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F180" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="G180" s="0">
+        <v>0.79</v>
+      </c>
+      <c r="H180" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="I180" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J180" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C181" s="0">
+        <v>1</v>
+      </c>
+      <c r="D181" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E181" s="0">
+        <v>1</v>
+      </c>
+      <c r="F181" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G181" s="0">
+        <v>1</v>
+      </c>
+      <c r="H181" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I181" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J181" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C182" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D182" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E182" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F182" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G182" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H182" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I182" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J182" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C183" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D183" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E183" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F183" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="G183" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H183" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="I183" s="0">
+        <v>0.55</v>
+      </c>
+      <c r="J183" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C184" s="0">
+        <v>0</v>
+      </c>
+      <c r="D184" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E184" s="0">
+        <v>0</v>
+      </c>
+      <c r="F184" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G184" s="0">
+        <v>0</v>
+      </c>
+      <c r="H184" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="I184" s="0">
+        <v>0</v>
+      </c>
+      <c r="J184" s="0" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -444,6 +444,102 @@
   </si>
   <si>
     <t>Testlauf 11 - 2026-09-26 21:55:45</t>
+  </si>
+  <si>
+    <t>Testlauf 12 - 2026-09-27 20:09:38</t>
+  </si>
+  <si>
+    <t>(377/457)</t>
+  </si>
+  <si>
+    <t>(1827/2792)</t>
+  </si>
+  <si>
+    <t>(7407/12453)</t>
+  </si>
+  <si>
+    <t>(3286/6255)</t>
+  </si>
+  <si>
+    <t>cli</t>
+  </si>
+  <si>
+    <t>(9/9)</t>
+  </si>
+  <si>
+    <t>(23/23)</t>
+  </si>
+  <si>
+    <t>(27/27)</t>
+  </si>
+  <si>
+    <t>(132/202)</t>
+  </si>
+  <si>
+    <t>(455/1228)</t>
+  </si>
+  <si>
+    <t>(2179/5531)</t>
+  </si>
+  <si>
+    <t>(779/2110)</t>
+  </si>
+  <si>
+    <t>(160/164)</t>
+  </si>
+  <si>
+    <t>(767/883)</t>
+  </si>
+  <si>
+    <t>(3067/4247)</t>
+  </si>
+  <si>
+    <t>(1466/2531)</t>
+  </si>
+  <si>
+    <t>(11/13)</t>
+  </si>
+  <si>
+    <t>(108/131)</t>
+  </si>
+  <si>
+    <t>(390/507)</t>
+  </si>
+  <si>
+    <t>(185/276)</t>
+  </si>
+  <si>
+    <t>(228/258)</t>
+  </si>
+  <si>
+    <t>(915/1097)</t>
+  </si>
+  <si>
+    <t>(472/737)</t>
+  </si>
+  <si>
+    <t>(8/8)</t>
+  </si>
+  <si>
+    <t>(28/31)</t>
+  </si>
+  <si>
+    <t>(115/160)</t>
+  </si>
+  <si>
+    <t>(22/54)</t>
+  </si>
+  <si>
+    <t>(88/102)</t>
+  </si>
+  <si>
+    <t>(290/407)</t>
+  </si>
+  <si>
+    <t>(161/286)</t>
+  </si>
+  <si>
+    <t>(0/22)</t>
   </si>
 </sst>
 </file>
@@ -489,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -4573,6 +4669,405 @@
         <v>65</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C189" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E189" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G189" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I189" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D190" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="E190" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F190" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="G190" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H190" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="I190" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J190" s="0" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C191" s="0">
+        <v>1</v>
+      </c>
+      <c r="D191" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E191" s="0">
+        <v>1</v>
+      </c>
+      <c r="F191" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G191" s="0">
+        <v>1</v>
+      </c>
+      <c r="H191" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I191" s="0">
+        <v>1</v>
+      </c>
+      <c r="J191" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" s="0">
+        <v>1</v>
+      </c>
+      <c r="D192" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E192" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F192" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G192" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H192" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I192" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J192" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="D193" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E193" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F193" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G193" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H193" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="I193" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J193" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C194" s="0">
+        <v>1</v>
+      </c>
+      <c r="D194" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E194" s="0">
+        <v>1</v>
+      </c>
+      <c r="F194" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G194" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H194" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I194" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J194" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C195" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D195" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="E195" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F195" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="G195" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H195" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="I195" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J195" s="0" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C196" s="0">
+        <v>1</v>
+      </c>
+      <c r="D196" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E196" s="0">
+        <v>1</v>
+      </c>
+      <c r="F196" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G196" s="0">
+        <v>1</v>
+      </c>
+      <c r="H196" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I196" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J196" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C197" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D197" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E197" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="F197" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="G197" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="H197" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="I197" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J197" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C198" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D198" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E198" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F198" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G198" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H198" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="I198" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J198" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C199" s="0">
+        <v>1</v>
+      </c>
+      <c r="D199" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E199" s="0">
+        <v>1</v>
+      </c>
+      <c r="F199" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G199" s="0">
+        <v>1</v>
+      </c>
+      <c r="H199" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I199" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J199" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C200" s="0">
+        <v>1</v>
+      </c>
+      <c r="D200" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E200" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F200" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G200" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H200" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I200" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J200" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C201" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D201" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E201" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F201" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G201" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H201" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I201" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J201" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C202" s="0">
+        <v>0</v>
+      </c>
+      <c r="D202" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E202" s="0">
+        <v>0</v>
+      </c>
+      <c r="F202" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G202" s="0">
+        <v>0</v>
+      </c>
+      <c r="H202" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="I202" s="0">
+        <v>0</v>
+      </c>
+      <c r="J202" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -540,6 +540,57 @@
   </si>
   <si>
     <t>(0/22)</t>
+  </si>
+  <si>
+    <t>Testlauf 13 - 2026-10-01 13:24:52</t>
+  </si>
+  <si>
+    <t>(354/463)</t>
+  </si>
+  <si>
+    <t>(1725/2855)</t>
+  </si>
+  <si>
+    <t>(6931/12959)</t>
+  </si>
+  <si>
+    <t>(3160/6428)</t>
+  </si>
+  <si>
+    <t>(130/206)</t>
+  </si>
+  <si>
+    <t>(459/1248)</t>
+  </si>
+  <si>
+    <t>(2225/5635)</t>
+  </si>
+  <si>
+    <t>(799/2153)</t>
+  </si>
+  <si>
+    <t>(144/166)</t>
+  </si>
+  <si>
+    <t>(677/925)</t>
+  </si>
+  <si>
+    <t>(2627/4640)</t>
+  </si>
+  <si>
+    <t>(1336/2661)</t>
+  </si>
+  <si>
+    <t>(109/132)</t>
+  </si>
+  <si>
+    <t>(393/516)</t>
+  </si>
+  <si>
+    <t>(227/258)</t>
+  </si>
+  <si>
+    <t>(911/1097)</t>
   </si>
 </sst>
 </file>
@@ -585,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -5068,6 +5119,405 @@
         <v>63</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="0" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C207" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E207" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G207" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I207" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="D208" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="E208" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="F208" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="G208" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="H208" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="I208" s="0">
+        <v>0.49</v>
+      </c>
+      <c r="J208" s="0" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C209" s="0">
+        <v>1</v>
+      </c>
+      <c r="D209" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E209" s="0">
+        <v>1</v>
+      </c>
+      <c r="F209" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G209" s="0">
+        <v>1</v>
+      </c>
+      <c r="H209" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I209" s="0">
+        <v>1</v>
+      </c>
+      <c r="J209" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="0">
+        <v>1</v>
+      </c>
+      <c r="D210" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E210" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F210" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G210" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H210" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I210" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J210" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C211" s="0">
+        <v>0.63</v>
+      </c>
+      <c r="D211" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="E211" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F211" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="G211" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H211" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="I211" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J211" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C212" s="0">
+        <v>1</v>
+      </c>
+      <c r="D212" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E212" s="0">
+        <v>1</v>
+      </c>
+      <c r="F212" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G212" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H212" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I212" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J212" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C213" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="D213" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="E213" s="0">
+        <v>0.73</v>
+      </c>
+      <c r="F213" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="G213" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="H213" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="I213" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J213" s="0" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C214" s="0">
+        <v>1</v>
+      </c>
+      <c r="D214" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E214" s="0">
+        <v>1</v>
+      </c>
+      <c r="F214" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G214" s="0">
+        <v>1</v>
+      </c>
+      <c r="H214" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I214" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J214" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C215" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D215" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E215" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="F215" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="G215" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="H215" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="I215" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J215" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C216" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D216" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E216" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F216" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G216" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H216" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I216" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J216" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C217" s="0">
+        <v>1</v>
+      </c>
+      <c r="D217" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E217" s="0">
+        <v>1</v>
+      </c>
+      <c r="F217" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G217" s="0">
+        <v>1</v>
+      </c>
+      <c r="H217" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I217" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J217" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C218" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="D218" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E218" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="F218" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G218" s="0">
+        <v>0.21</v>
+      </c>
+      <c r="H218" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="I218" s="0">
+        <v>0.11</v>
+      </c>
+      <c r="J218" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C219" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D219" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E219" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F219" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G219" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H219" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I219" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J219" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C220" s="0">
+        <v>0</v>
+      </c>
+      <c r="D220" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E220" s="0">
+        <v>0</v>
+      </c>
+      <c r="F220" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G220" s="0">
+        <v>0</v>
+      </c>
+      <c r="H220" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="I220" s="0">
+        <v>0</v>
+      </c>
+      <c r="J220" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -591,6 +591,174 @@
   </si>
   <si>
     <t>(911/1097)</t>
+  </si>
+  <si>
+    <t>Testlauf 14 - 2026-10-01 20:48:29</t>
+  </si>
+  <si>
+    <t>(384/463)</t>
+  </si>
+  <si>
+    <t>(1884/2860)</t>
+  </si>
+  <si>
+    <t>(7729/12976)</t>
+  </si>
+  <si>
+    <t>(3406/6428)</t>
+  </si>
+  <si>
+    <t>(137/206)</t>
+  </si>
+  <si>
+    <t>(469/1248)</t>
+  </si>
+  <si>
+    <t>(2247/5635)</t>
+  </si>
+  <si>
+    <t>(803/2153)</t>
+  </si>
+  <si>
+    <t>(162/166)</t>
+  </si>
+  <si>
+    <t>(809/928)</t>
+  </si>
+  <si>
+    <t>(3320/4648)</t>
+  </si>
+  <si>
+    <t>(1562/2661)</t>
+  </si>
+  <si>
+    <t>(109/134)</t>
+  </si>
+  <si>
+    <t>(393/525)</t>
+  </si>
+  <si>
+    <t>(913/1097)</t>
+  </si>
+  <si>
+    <t>Testlauf 15 - 2026-10-01 21:05:20</t>
+  </si>
+  <si>
+    <t>(378/463)</t>
+  </si>
+  <si>
+    <t>(1874/2860)</t>
+  </si>
+  <si>
+    <t>(7694/12976)</t>
+  </si>
+  <si>
+    <t>(3394/6428)</t>
+  </si>
+  <si>
+    <t>(131/206)</t>
+  </si>
+  <si>
+    <t>(461/1248)</t>
+  </si>
+  <si>
+    <t>(2227/5635)</t>
+  </si>
+  <si>
+    <t>(807/928)</t>
+  </si>
+  <si>
+    <t>(3305/4648)</t>
+  </si>
+  <si>
+    <t>(1557/2661)</t>
+  </si>
+  <si>
+    <t>(182/276)</t>
+  </si>
+  <si>
+    <t>Testlauf 16 - 2026-10-01 21:18:03</t>
+  </si>
+  <si>
+    <t>(1875/2860)</t>
+  </si>
+  <si>
+    <t>(7700/12976)</t>
+  </si>
+  <si>
+    <t>(3396/6428)</t>
+  </si>
+  <si>
+    <t>(808/928)</t>
+  </si>
+  <si>
+    <t>(3311/4648)</t>
+  </si>
+  <si>
+    <t>(1559/2661)</t>
+  </si>
+  <si>
+    <t>Testlauf 17 - 2026-10-01 21:30:07</t>
+  </si>
+  <si>
+    <t>(1870/2860)</t>
+  </si>
+  <si>
+    <t>(7684/12976)</t>
+  </si>
+  <si>
+    <t>(3392/6428)</t>
+  </si>
+  <si>
+    <t>(800/2153)</t>
+  </si>
+  <si>
+    <t>(803/928)</t>
+  </si>
+  <si>
+    <t>(3295/4648)</t>
+  </si>
+  <si>
+    <t>(1551/2661)</t>
+  </si>
+  <si>
+    <t>Testlauf 18 - 2026-10-01 22:00:16</t>
+  </si>
+  <si>
+    <t>(379/463)</t>
+  </si>
+  <si>
+    <t>(1872/2860)</t>
+  </si>
+  <si>
+    <t>(7692/12976)</t>
+  </si>
+  <si>
+    <t>(3391/6428)</t>
+  </si>
+  <si>
+    <t>(3296/4648)</t>
+  </si>
+  <si>
+    <t>(1552/2661)</t>
+  </si>
+  <si>
+    <t>(1/1)</t>
+  </si>
+  <si>
+    <t>(2/4)</t>
+  </si>
+  <si>
+    <t>(7/22)</t>
+  </si>
+  <si>
+    <t>Testlauf 19 - 2026-10-01 22:14:11</t>
+  </si>
+  <si>
+    <t>(3393/6428)</t>
+  </si>
+  <si>
+    <t>(1554/2661)</t>
   </si>
 </sst>
 </file>
@@ -636,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J220"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -5518,6 +5686,2400 @@
         <v>63</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="0" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C225" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E225" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G225" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I225" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C226" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D226" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="E226" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F226" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="G226" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="H226" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="I226" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J226" s="0" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C227" s="0">
+        <v>1</v>
+      </c>
+      <c r="D227" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E227" s="0">
+        <v>1</v>
+      </c>
+      <c r="F227" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G227" s="0">
+        <v>1</v>
+      </c>
+      <c r="H227" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I227" s="0">
+        <v>1</v>
+      </c>
+      <c r="J227" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" s="0">
+        <v>1</v>
+      </c>
+      <c r="D228" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E228" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F228" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G228" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H228" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I228" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J228" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C229" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D229" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="E229" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="F229" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="G229" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H229" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="I229" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J229" s="0" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C230" s="0">
+        <v>1</v>
+      </c>
+      <c r="D230" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E230" s="0">
+        <v>1</v>
+      </c>
+      <c r="F230" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G230" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H230" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I230" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J230" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C231" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D231" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E231" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F231" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="G231" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H231" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="I231" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J231" s="0" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C232" s="0">
+        <v>1</v>
+      </c>
+      <c r="D232" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E232" s="0">
+        <v>1</v>
+      </c>
+      <c r="F232" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G232" s="0">
+        <v>1</v>
+      </c>
+      <c r="H232" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I232" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J232" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C233" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D233" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E233" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F233" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G233" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H233" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I233" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J233" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C234" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D234" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E234" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F234" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G234" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H234" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I234" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J234" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C235" s="0">
+        <v>1</v>
+      </c>
+      <c r="D235" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E235" s="0">
+        <v>1</v>
+      </c>
+      <c r="F235" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G235" s="0">
+        <v>1</v>
+      </c>
+      <c r="H235" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I235" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J235" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C236" s="0">
+        <v>1</v>
+      </c>
+      <c r="D236" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E236" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F236" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G236" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H236" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I236" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J236" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C237" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D237" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E237" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F237" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G237" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H237" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I237" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J237" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C238" s="0">
+        <v>0</v>
+      </c>
+      <c r="D238" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E238" s="0">
+        <v>0</v>
+      </c>
+      <c r="F238" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G238" s="0">
+        <v>0</v>
+      </c>
+      <c r="H238" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="I238" s="0">
+        <v>0</v>
+      </c>
+      <c r="J238" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C243" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E243" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G243" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I243" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C244" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D244" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="E244" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F244" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="G244" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H244" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="I244" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J244" s="0" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C245" s="0">
+        <v>1</v>
+      </c>
+      <c r="D245" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E245" s="0">
+        <v>1</v>
+      </c>
+      <c r="F245" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G245" s="0">
+        <v>1</v>
+      </c>
+      <c r="H245" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I245" s="0">
+        <v>1</v>
+      </c>
+      <c r="J245" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" s="0">
+        <v>1</v>
+      </c>
+      <c r="D246" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E246" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F246" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G246" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H246" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I246" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J246" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C247" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D247" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E247" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F247" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G247" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H247" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I247" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J247" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C248" s="0">
+        <v>1</v>
+      </c>
+      <c r="D248" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E248" s="0">
+        <v>1</v>
+      </c>
+      <c r="F248" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G248" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H248" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I248" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J248" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C249" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D249" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E249" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F249" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="G249" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H249" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="I249" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J249" s="0" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C250" s="0">
+        <v>1</v>
+      </c>
+      <c r="D250" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E250" s="0">
+        <v>1</v>
+      </c>
+      <c r="F250" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G250" s="0">
+        <v>1</v>
+      </c>
+      <c r="H250" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I250" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J250" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C251" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D251" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E251" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F251" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G251" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H251" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I251" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J251" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C252" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D252" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E252" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F252" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G252" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H252" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I252" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J252" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C253" s="0">
+        <v>1</v>
+      </c>
+      <c r="D253" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E253" s="0">
+        <v>1</v>
+      </c>
+      <c r="F253" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G253" s="0">
+        <v>1</v>
+      </c>
+      <c r="H253" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I253" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J253" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C254" s="0">
+        <v>1</v>
+      </c>
+      <c r="D254" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E254" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F254" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G254" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H254" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I254" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J254" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C255" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D255" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E255" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F255" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G255" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H255" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I255" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J255" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C256" s="0">
+        <v>0</v>
+      </c>
+      <c r="D256" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E256" s="0">
+        <v>0</v>
+      </c>
+      <c r="F256" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G256" s="0">
+        <v>0</v>
+      </c>
+      <c r="H256" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="I256" s="0">
+        <v>0</v>
+      </c>
+      <c r="J256" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C261" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E261" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G261" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I261" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C262" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D262" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="E262" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F262" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="G262" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H262" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="I262" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J262" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C263" s="0">
+        <v>1</v>
+      </c>
+      <c r="D263" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E263" s="0">
+        <v>1</v>
+      </c>
+      <c r="F263" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G263" s="0">
+        <v>1</v>
+      </c>
+      <c r="H263" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I263" s="0">
+        <v>1</v>
+      </c>
+      <c r="J263" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" s="0">
+        <v>1</v>
+      </c>
+      <c r="D264" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E264" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F264" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G264" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H264" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I264" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J264" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C265" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D265" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E265" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F265" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G265" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H265" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I265" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J265" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C266" s="0">
+        <v>1</v>
+      </c>
+      <c r="D266" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E266" s="0">
+        <v>1</v>
+      </c>
+      <c r="F266" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G266" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H266" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I266" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J266" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C267" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D267" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E267" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F267" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="G267" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H267" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="I267" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="J267" s="0" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C268" s="0">
+        <v>1</v>
+      </c>
+      <c r="D268" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E268" s="0">
+        <v>1</v>
+      </c>
+      <c r="F268" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G268" s="0">
+        <v>1</v>
+      </c>
+      <c r="H268" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I268" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J268" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C269" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D269" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E269" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F269" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G269" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H269" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I269" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J269" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C270" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D270" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E270" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F270" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G270" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H270" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I270" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J270" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C271" s="0">
+        <v>1</v>
+      </c>
+      <c r="D271" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E271" s="0">
+        <v>1</v>
+      </c>
+      <c r="F271" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G271" s="0">
+        <v>1</v>
+      </c>
+      <c r="H271" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I271" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J271" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C272" s="0">
+        <v>1</v>
+      </c>
+      <c r="D272" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E272" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F272" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G272" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H272" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I272" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J272" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C273" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D273" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E273" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F273" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G273" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H273" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I273" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J273" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C274" s="0">
+        <v>0</v>
+      </c>
+      <c r="D274" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E274" s="0">
+        <v>0</v>
+      </c>
+      <c r="F274" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G274" s="0">
+        <v>0</v>
+      </c>
+      <c r="H274" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="I274" s="0">
+        <v>0</v>
+      </c>
+      <c r="J274" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C279" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E279" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G279" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I279" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D280" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="E280" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F280" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="G280" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H280" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="I280" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J280" s="0" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C281" s="0">
+        <v>1</v>
+      </c>
+      <c r="D281" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E281" s="0">
+        <v>1</v>
+      </c>
+      <c r="F281" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G281" s="0">
+        <v>1</v>
+      </c>
+      <c r="H281" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I281" s="0">
+        <v>1</v>
+      </c>
+      <c r="J281" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C282" s="0">
+        <v>1</v>
+      </c>
+      <c r="D282" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E282" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F282" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G282" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H282" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I282" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J282" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C283" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D283" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E283" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F283" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G283" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H283" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I283" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J283" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C284" s="0">
+        <v>1</v>
+      </c>
+      <c r="D284" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E284" s="0">
+        <v>1</v>
+      </c>
+      <c r="F284" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G284" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H284" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I284" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J284" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C285" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D285" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E285" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F285" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G285" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H285" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="I285" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J285" s="0" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C286" s="0">
+        <v>1</v>
+      </c>
+      <c r="D286" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E286" s="0">
+        <v>1</v>
+      </c>
+      <c r="F286" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G286" s="0">
+        <v>1</v>
+      </c>
+      <c r="H286" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I286" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J286" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C287" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D287" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E287" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F287" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G287" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H287" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I287" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J287" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C288" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D288" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E288" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F288" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G288" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H288" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I288" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J288" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C289" s="0">
+        <v>1</v>
+      </c>
+      <c r="D289" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E289" s="0">
+        <v>1</v>
+      </c>
+      <c r="F289" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G289" s="0">
+        <v>1</v>
+      </c>
+      <c r="H289" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I289" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J289" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C290" s="0">
+        <v>1</v>
+      </c>
+      <c r="D290" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E290" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F290" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G290" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H290" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I290" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J290" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C291" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D291" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E291" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F291" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G291" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H291" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I291" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J291" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C292" s="0">
+        <v>0</v>
+      </c>
+      <c r="D292" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="E292" s="0">
+        <v>0</v>
+      </c>
+      <c r="F292" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="G292" s="0">
+        <v>0</v>
+      </c>
+      <c r="H292" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="I292" s="0">
+        <v>0</v>
+      </c>
+      <c r="J292" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C297" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E297" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G297" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I297" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C298" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D298" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E298" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F298" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="G298" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H298" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="I298" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J298" s="0" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C299" s="0">
+        <v>1</v>
+      </c>
+      <c r="D299" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E299" s="0">
+        <v>1</v>
+      </c>
+      <c r="F299" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G299" s="0">
+        <v>1</v>
+      </c>
+      <c r="H299" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I299" s="0">
+        <v>1</v>
+      </c>
+      <c r="J299" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" s="0">
+        <v>1</v>
+      </c>
+      <c r="D300" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E300" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F300" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G300" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H300" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I300" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J300" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C301" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D301" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E301" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F301" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G301" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H301" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I301" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J301" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C302" s="0">
+        <v>1</v>
+      </c>
+      <c r="D302" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E302" s="0">
+        <v>1</v>
+      </c>
+      <c r="F302" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G302" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H302" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I302" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J302" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C303" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D303" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E303" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F303" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G303" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H303" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I303" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J303" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C304" s="0">
+        <v>1</v>
+      </c>
+      <c r="D304" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E304" s="0">
+        <v>1</v>
+      </c>
+      <c r="F304" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G304" s="0">
+        <v>1</v>
+      </c>
+      <c r="H304" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I304" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J304" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C305" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D305" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E305" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F305" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G305" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H305" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I305" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J305" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C306" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D306" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E306" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F306" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G306" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H306" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I306" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J306" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C307" s="0">
+        <v>1</v>
+      </c>
+      <c r="D307" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E307" s="0">
+        <v>1</v>
+      </c>
+      <c r="F307" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G307" s="0">
+        <v>1</v>
+      </c>
+      <c r="H307" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I307" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J307" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C308" s="0">
+        <v>1</v>
+      </c>
+      <c r="D308" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E308" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F308" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G308" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H308" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I308" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J308" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C309" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D309" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E309" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F309" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G309" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H309" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I309" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J309" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C310" s="0">
+        <v>1</v>
+      </c>
+      <c r="D310" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E310" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F310" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G310" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H310" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I310" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J310" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C315" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E315" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G315" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I315" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C316" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D316" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E316" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F316" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="G316" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H316" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="I316" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J316" s="0" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C317" s="0">
+        <v>1</v>
+      </c>
+      <c r="D317" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E317" s="0">
+        <v>1</v>
+      </c>
+      <c r="F317" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G317" s="0">
+        <v>1</v>
+      </c>
+      <c r="H317" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I317" s="0">
+        <v>1</v>
+      </c>
+      <c r="J317" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318" s="0">
+        <v>1</v>
+      </c>
+      <c r="D318" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E318" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F318" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G318" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H318" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I318" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J318" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C319" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D319" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E319" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F319" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G319" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H319" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I319" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J319" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C320" s="0">
+        <v>1</v>
+      </c>
+      <c r="D320" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E320" s="0">
+        <v>1</v>
+      </c>
+      <c r="F320" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G320" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H320" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I320" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J320" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C321" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D321" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E321" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F321" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G321" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H321" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I321" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J321" s="0" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C322" s="0">
+        <v>1</v>
+      </c>
+      <c r="D322" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E322" s="0">
+        <v>1</v>
+      </c>
+      <c r="F322" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G322" s="0">
+        <v>1</v>
+      </c>
+      <c r="H322" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I322" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J322" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C323" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D323" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E323" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F323" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G323" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H323" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I323" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J323" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C324" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D324" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E324" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F324" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G324" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H324" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I324" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J324" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C325" s="0">
+        <v>1</v>
+      </c>
+      <c r="D325" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E325" s="0">
+        <v>1</v>
+      </c>
+      <c r="F325" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G325" s="0">
+        <v>1</v>
+      </c>
+      <c r="H325" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I325" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J325" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C326" s="0">
+        <v>1</v>
+      </c>
+      <c r="D326" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E326" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F326" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G326" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H326" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I326" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J326" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C327" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D327" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E327" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F327" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G327" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H327" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I327" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J327" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C328" s="0">
+        <v>1</v>
+      </c>
+      <c r="D328" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E328" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F328" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G328" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H328" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I328" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J328" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -759,6 +759,27 @@
   </si>
   <si>
     <t>(1554/2661)</t>
+  </si>
+  <si>
+    <t>Testlauf 20 - 2026-10-01 22:42:35</t>
+  </si>
+  <si>
+    <t>(7691/12976)</t>
+  </si>
+  <si>
+    <t>(3397/6428)</t>
+  </si>
+  <si>
+    <t>Testlauf 21 - 2026-10-01 22:51:17</t>
+  </si>
+  <si>
+    <t>(1553/2661)</t>
+  </si>
+  <si>
+    <t>Testlauf 22 - 2026-10-01 23:06:14</t>
+  </si>
+  <si>
+    <t>(3395/6428)</t>
   </si>
 </sst>
 </file>
@@ -804,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -8080,6 +8101,1203 @@
         <v>244</v>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" s="0" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C333" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E333" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G333" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I333" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C334" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D334" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E334" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F334" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="G334" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H334" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="I334" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J334" s="0" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C335" s="0">
+        <v>1</v>
+      </c>
+      <c r="D335" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E335" s="0">
+        <v>1</v>
+      </c>
+      <c r="F335" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G335" s="0">
+        <v>1</v>
+      </c>
+      <c r="H335" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I335" s="0">
+        <v>1</v>
+      </c>
+      <c r="J335" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C336" s="0">
+        <v>1</v>
+      </c>
+      <c r="D336" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E336" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F336" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G336" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H336" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I336" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J336" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C337" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D337" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E337" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F337" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G337" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H337" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I337" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J337" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C338" s="0">
+        <v>1</v>
+      </c>
+      <c r="D338" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E338" s="0">
+        <v>1</v>
+      </c>
+      <c r="F338" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G338" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H338" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I338" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J338" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C339" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D339" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E339" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F339" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G339" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H339" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="I339" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J339" s="0" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C340" s="0">
+        <v>1</v>
+      </c>
+      <c r="D340" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E340" s="0">
+        <v>1</v>
+      </c>
+      <c r="F340" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G340" s="0">
+        <v>1</v>
+      </c>
+      <c r="H340" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I340" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J340" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C341" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D341" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E341" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F341" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G341" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H341" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I341" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J341" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C342" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D342" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E342" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F342" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G342" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H342" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I342" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J342" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C343" s="0">
+        <v>1</v>
+      </c>
+      <c r="D343" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E343" s="0">
+        <v>1</v>
+      </c>
+      <c r="F343" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G343" s="0">
+        <v>1</v>
+      </c>
+      <c r="H343" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I343" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J343" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C344" s="0">
+        <v>1</v>
+      </c>
+      <c r="D344" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E344" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F344" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G344" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H344" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I344" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J344" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C345" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D345" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E345" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F345" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G345" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H345" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I345" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J345" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C346" s="0">
+        <v>1</v>
+      </c>
+      <c r="D346" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E346" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F346" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G346" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H346" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I346" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J346" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="0" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C351" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E351" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G351" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I351" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C352" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D352" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E352" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F352" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="G352" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H352" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="I352" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J352" s="0" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C353" s="0">
+        <v>1</v>
+      </c>
+      <c r="D353" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E353" s="0">
+        <v>1</v>
+      </c>
+      <c r="F353" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G353" s="0">
+        <v>1</v>
+      </c>
+      <c r="H353" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I353" s="0">
+        <v>1</v>
+      </c>
+      <c r="J353" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C354" s="0">
+        <v>1</v>
+      </c>
+      <c r="D354" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E354" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F354" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G354" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H354" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I354" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J354" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C355" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D355" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E355" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F355" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G355" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H355" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I355" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J355" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C356" s="0">
+        <v>1</v>
+      </c>
+      <c r="D356" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E356" s="0">
+        <v>1</v>
+      </c>
+      <c r="F356" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G356" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H356" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I356" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J356" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C357" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D357" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E357" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F357" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G357" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H357" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I357" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J357" s="0" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C358" s="0">
+        <v>1</v>
+      </c>
+      <c r="D358" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E358" s="0">
+        <v>1</v>
+      </c>
+      <c r="F358" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G358" s="0">
+        <v>1</v>
+      </c>
+      <c r="H358" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I358" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J358" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C359" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D359" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E359" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F359" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G359" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H359" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I359" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J359" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C360" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D360" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E360" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F360" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G360" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H360" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I360" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J360" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C361" s="0">
+        <v>1</v>
+      </c>
+      <c r="D361" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E361" s="0">
+        <v>1</v>
+      </c>
+      <c r="F361" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G361" s="0">
+        <v>1</v>
+      </c>
+      <c r="H361" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I361" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J361" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C362" s="0">
+        <v>1</v>
+      </c>
+      <c r="D362" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E362" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F362" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G362" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H362" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I362" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J362" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C363" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D363" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E363" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F363" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G363" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H363" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I363" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J363" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C364" s="0">
+        <v>1</v>
+      </c>
+      <c r="D364" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E364" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F364" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G364" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H364" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I364" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J364" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C369" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E369" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G369" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I369" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C370" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D370" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E370" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F370" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="G370" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H370" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="I370" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J370" s="0" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C371" s="0">
+        <v>1</v>
+      </c>
+      <c r="D371" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E371" s="0">
+        <v>1</v>
+      </c>
+      <c r="F371" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G371" s="0">
+        <v>1</v>
+      </c>
+      <c r="H371" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I371" s="0">
+        <v>1</v>
+      </c>
+      <c r="J371" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C372" s="0">
+        <v>1</v>
+      </c>
+      <c r="D372" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E372" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F372" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G372" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H372" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I372" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J372" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C373" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D373" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E373" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F373" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G373" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H373" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I373" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J373" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C374" s="0">
+        <v>1</v>
+      </c>
+      <c r="D374" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E374" s="0">
+        <v>1</v>
+      </c>
+      <c r="F374" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G374" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H374" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I374" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J374" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C375" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D375" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E375" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F375" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G375" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H375" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I375" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J375" s="0" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C376" s="0">
+        <v>1</v>
+      </c>
+      <c r="D376" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E376" s="0">
+        <v>1</v>
+      </c>
+      <c r="F376" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G376" s="0">
+        <v>1</v>
+      </c>
+      <c r="H376" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I376" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J376" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C377" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D377" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E377" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F377" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G377" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H377" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I377" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J377" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C378" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D378" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E378" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F378" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G378" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H378" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I378" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J378" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C379" s="0">
+        <v>1</v>
+      </c>
+      <c r="D379" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E379" s="0">
+        <v>1</v>
+      </c>
+      <c r="F379" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G379" s="0">
+        <v>1</v>
+      </c>
+      <c r="H379" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I379" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J379" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C380" s="0">
+        <v>1</v>
+      </c>
+      <c r="D380" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E380" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F380" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G380" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H380" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I380" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J380" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C381" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D381" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E381" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F381" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G381" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H381" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I381" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J381" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C382" s="0">
+        <v>1</v>
+      </c>
+      <c r="D382" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E382" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F382" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G382" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H382" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I382" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J382" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -780,6 +780,21 @@
   </si>
   <si>
     <t>(3395/6428)</t>
+  </si>
+  <si>
+    <t>Testlauf 23 - 2026-10-01 23:22:23</t>
+  </si>
+  <si>
+    <t>Testlauf 24 - 2026-10-01 23:33:56</t>
+  </si>
+  <si>
+    <t>(385/463)</t>
+  </si>
+  <si>
+    <t>(1880/2860)</t>
+  </si>
+  <si>
+    <t>(7712/12976)</t>
   </si>
 </sst>
 </file>
@@ -825,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J418"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -9298,6 +9313,804 @@
         <v>244</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="0" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C387" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E387" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G387" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I387" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C388" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D388" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E388" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F388" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="G388" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H388" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="I388" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J388" s="0" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C389" s="0">
+        <v>1</v>
+      </c>
+      <c r="D389" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E389" s="0">
+        <v>1</v>
+      </c>
+      <c r="F389" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G389" s="0">
+        <v>1</v>
+      </c>
+      <c r="H389" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I389" s="0">
+        <v>1</v>
+      </c>
+      <c r="J389" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C390" s="0">
+        <v>1</v>
+      </c>
+      <c r="D390" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E390" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F390" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G390" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H390" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I390" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J390" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C391" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D391" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E391" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F391" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G391" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H391" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I391" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J391" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C392" s="0">
+        <v>1</v>
+      </c>
+      <c r="D392" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E392" s="0">
+        <v>1</v>
+      </c>
+      <c r="F392" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G392" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H392" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I392" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J392" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C393" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D393" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E393" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F393" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G393" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H393" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I393" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J393" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C394" s="0">
+        <v>1</v>
+      </c>
+      <c r="D394" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E394" s="0">
+        <v>1</v>
+      </c>
+      <c r="F394" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G394" s="0">
+        <v>1</v>
+      </c>
+      <c r="H394" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I394" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J394" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C395" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D395" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E395" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F395" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G395" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H395" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I395" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J395" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C396" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D396" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E396" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F396" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G396" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H396" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I396" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J396" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C397" s="0">
+        <v>1</v>
+      </c>
+      <c r="D397" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E397" s="0">
+        <v>1</v>
+      </c>
+      <c r="F397" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G397" s="0">
+        <v>1</v>
+      </c>
+      <c r="H397" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I397" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J397" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C398" s="0">
+        <v>1</v>
+      </c>
+      <c r="D398" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E398" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F398" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G398" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H398" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I398" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J398" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C399" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D399" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E399" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F399" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G399" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H399" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I399" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J399" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C400" s="0">
+        <v>1</v>
+      </c>
+      <c r="D400" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E400" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F400" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G400" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H400" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I400" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J400" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C405" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E405" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G405" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I405" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C406" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D406" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="E406" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F406" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="G406" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H406" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="I406" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J406" s="0" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C407" s="0">
+        <v>1</v>
+      </c>
+      <c r="D407" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E407" s="0">
+        <v>1</v>
+      </c>
+      <c r="F407" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G407" s="0">
+        <v>1</v>
+      </c>
+      <c r="H407" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I407" s="0">
+        <v>1</v>
+      </c>
+      <c r="J407" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C408" s="0">
+        <v>1</v>
+      </c>
+      <c r="D408" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E408" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F408" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G408" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H408" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I408" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J408" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C409" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="D409" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="E409" s="0">
+        <v>0.38</v>
+      </c>
+      <c r="F409" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="G409" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H409" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="I409" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J409" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C410" s="0">
+        <v>1</v>
+      </c>
+      <c r="D410" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E410" s="0">
+        <v>1</v>
+      </c>
+      <c r="F410" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G410" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H410" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I410" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J410" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C411" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D411" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E411" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F411" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="G411" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H411" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="I411" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J411" s="0" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C412" s="0">
+        <v>1</v>
+      </c>
+      <c r="D412" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E412" s="0">
+        <v>1</v>
+      </c>
+      <c r="F412" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G412" s="0">
+        <v>1</v>
+      </c>
+      <c r="H412" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I412" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J412" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C413" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D413" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E413" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F413" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G413" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H413" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I413" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J413" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C414" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D414" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E414" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F414" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G414" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H414" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I414" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J414" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C415" s="0">
+        <v>1</v>
+      </c>
+      <c r="D415" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E415" s="0">
+        <v>1</v>
+      </c>
+      <c r="F415" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G415" s="0">
+        <v>1</v>
+      </c>
+      <c r="H415" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I415" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J415" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C416" s="0">
+        <v>1</v>
+      </c>
+      <c r="D416" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E416" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F416" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G416" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H416" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I416" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J416" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C417" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D417" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E417" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F417" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="G417" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H417" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="I417" s="0">
+        <v>0.56</v>
+      </c>
+      <c r="J417" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C418" s="0">
+        <v>1</v>
+      </c>
+      <c r="D418" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E418" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F418" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G418" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H418" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I418" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J418" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="271">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -795,6 +795,36 @@
   </si>
   <si>
     <t>(7712/12976)</t>
+  </si>
+  <si>
+    <t>Testlauf 25 - 2026-10-02 07:45:01</t>
+  </si>
+  <si>
+    <t>(1875/2862)</t>
+  </si>
+  <si>
+    <t>(7728/13005)</t>
+  </si>
+  <si>
+    <t>(3421/6472)</t>
+  </si>
+  <si>
+    <t>(804/928)</t>
+  </si>
+  <si>
+    <t>(3318/4663)</t>
+  </si>
+  <si>
+    <t>(1568/2685)</t>
+  </si>
+  <si>
+    <t>(90/104)</t>
+  </si>
+  <si>
+    <t>(304/421)</t>
+  </si>
+  <si>
+    <t>(174/306)</t>
   </si>
 </sst>
 </file>
@@ -840,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J418"/>
+  <dimension ref="A1:J436"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -10111,6 +10141,405 @@
         <v>244</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="0" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C423" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E423" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G423" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I423" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C424" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D424" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E424" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F424" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="G424" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H424" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="I424" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J424" s="0" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C425" s="0">
+        <v>1</v>
+      </c>
+      <c r="D425" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E425" s="0">
+        <v>1</v>
+      </c>
+      <c r="F425" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G425" s="0">
+        <v>1</v>
+      </c>
+      <c r="H425" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I425" s="0">
+        <v>1</v>
+      </c>
+      <c r="J425" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C426" s="0">
+        <v>1</v>
+      </c>
+      <c r="D426" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E426" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F426" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G426" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H426" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I426" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J426" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C427" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D427" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E427" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F427" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G427" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H427" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I427" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J427" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C428" s="0">
+        <v>1</v>
+      </c>
+      <c r="D428" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E428" s="0">
+        <v>1</v>
+      </c>
+      <c r="F428" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G428" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H428" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I428" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J428" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C429" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D429" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E429" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F429" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="G429" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H429" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="I429" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J429" s="0" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C430" s="0">
+        <v>1</v>
+      </c>
+      <c r="D430" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E430" s="0">
+        <v>1</v>
+      </c>
+      <c r="F430" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G430" s="0">
+        <v>1</v>
+      </c>
+      <c r="H430" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I430" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J430" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C431" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D431" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E431" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F431" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G431" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H431" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I431" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J431" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C432" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D432" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E432" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F432" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G432" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H432" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I432" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J432" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C433" s="0">
+        <v>1</v>
+      </c>
+      <c r="D433" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E433" s="0">
+        <v>1</v>
+      </c>
+      <c r="F433" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G433" s="0">
+        <v>1</v>
+      </c>
+      <c r="H433" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I433" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J433" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C434" s="0">
+        <v>1</v>
+      </c>
+      <c r="D434" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E434" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F434" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G434" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H434" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I434" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J434" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C435" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D435" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E435" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F435" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G435" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H435" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I435" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J435" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C436" s="0">
+        <v>1</v>
+      </c>
+      <c r="D436" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E436" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F436" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G436" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H436" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I436" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J436" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -825,6 +825,330 @@
   </si>
   <si>
     <t>(174/306)</t>
+  </si>
+  <si>
+    <t>Testlauf 26 - 2026-10-06 18:18:41</t>
+  </si>
+  <si>
+    <t>(344/463)</t>
+  </si>
+  <si>
+    <t>(1649/2862)</t>
+  </si>
+  <si>
+    <t>(6614/13005)</t>
+  </si>
+  <si>
+    <t>(3040/6472)</t>
+  </si>
+  <si>
+    <t>(128/206)</t>
+  </si>
+  <si>
+    <t>(456/1248)</t>
+  </si>
+  <si>
+    <t>(2198/5635)</t>
+  </si>
+  <si>
+    <t>(786/2153)</t>
+  </si>
+  <si>
+    <t>(138/166)</t>
+  </si>
+  <si>
+    <t>(614/928)</t>
+  </si>
+  <si>
+    <t>(2361/4663)</t>
+  </si>
+  <si>
+    <t>(1233/2685)</t>
+  </si>
+  <si>
+    <t>(0/8)</t>
+  </si>
+  <si>
+    <t>(0/31)</t>
+  </si>
+  <si>
+    <t>(0/160)</t>
+  </si>
+  <si>
+    <t>(0/54)</t>
+  </si>
+  <si>
+    <t>(88/104)</t>
+  </si>
+  <si>
+    <t>(293/421)</t>
+  </si>
+  <si>
+    <t>(161/306)</t>
+  </si>
+  <si>
+    <t>Testlauf 27 - 2026-10-06 18:49:42</t>
+  </si>
+  <si>
+    <t>(1858/2862)</t>
+  </si>
+  <si>
+    <t>(7626/13005)</t>
+  </si>
+  <si>
+    <t>(3370/6472)</t>
+  </si>
+  <si>
+    <t>(2217/5635)</t>
+  </si>
+  <si>
+    <t>(791/2153)</t>
+  </si>
+  <si>
+    <t>(799/928)</t>
+  </si>
+  <si>
+    <t>(3271/4663)</t>
+  </si>
+  <si>
+    <t>(1551/2685)</t>
+  </si>
+  <si>
+    <t>(97/134)</t>
+  </si>
+  <si>
+    <t>(348/525)</t>
+  </si>
+  <si>
+    <t>(157/276)</t>
+  </si>
+  <si>
+    <t>Testlauf 28 - 2026-10-06 18:55:23</t>
+  </si>
+  <si>
+    <t>(350/463)</t>
+  </si>
+  <si>
+    <t>(1657/2862)</t>
+  </si>
+  <si>
+    <t>(6636/13005)</t>
+  </si>
+  <si>
+    <t>(3037/6472)</t>
+  </si>
+  <si>
+    <t>(134/206)</t>
+  </si>
+  <si>
+    <t>(464/1248)</t>
+  </si>
+  <si>
+    <t>(2218/5635)</t>
+  </si>
+  <si>
+    <t>Testlauf 29 - 2026-10-06 19:01:40</t>
+  </si>
+  <si>
+    <t>(1635/2862)</t>
+  </si>
+  <si>
+    <t>(6572/13005)</t>
+  </si>
+  <si>
+    <t>(3012/6472)</t>
+  </si>
+  <si>
+    <t>(455/1248)</t>
+  </si>
+  <si>
+    <t>(2202/5635)</t>
+  </si>
+  <si>
+    <t>(226/258)</t>
+  </si>
+  <si>
+    <t>(910/1097)</t>
+  </si>
+  <si>
+    <t>Testlauf 30 - 2026-10-06 19:19:54</t>
+  </si>
+  <si>
+    <t>(3039/6472)</t>
+  </si>
+  <si>
+    <t>(785/2153)</t>
+  </si>
+  <si>
+    <t>Testlauf 31 - 2026-10-06 19:39:15</t>
+  </si>
+  <si>
+    <t>(1870/2862)</t>
+  </si>
+  <si>
+    <t>(7673/13005)</t>
+  </si>
+  <si>
+    <t>(3393/6472)</t>
+  </si>
+  <si>
+    <t>(1549/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 32 - 2026-10-06 23:33:50</t>
+  </si>
+  <si>
+    <t>(343/463)</t>
+  </si>
+  <si>
+    <t>(6564/13005)</t>
+  </si>
+  <si>
+    <t>(3009/6472)</t>
+  </si>
+  <si>
+    <t>(457/1248)</t>
+  </si>
+  <si>
+    <t>(137/166)</t>
+  </si>
+  <si>
+    <t>(611/928)</t>
+  </si>
+  <si>
+    <t>(2352/4663)</t>
+  </si>
+  <si>
+    <t>(1230/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 33 - 2026-10-06 23:46:38</t>
+  </si>
+  <si>
+    <t>(1637/2862)</t>
+  </si>
+  <si>
+    <t>(3011/6472)</t>
+  </si>
+  <si>
+    <t>(787/2153)</t>
+  </si>
+  <si>
+    <t>(613/928)</t>
+  </si>
+  <si>
+    <t>(2360/4663)</t>
+  </si>
+  <si>
+    <t>(1231/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 34 - 2026-10-07 10:52:33</t>
+  </si>
+  <si>
+    <t>(1873/2862)</t>
+  </si>
+  <si>
+    <t>(7707/13005)</t>
+  </si>
+  <si>
+    <t>(3425/6472)</t>
+  </si>
+  <si>
+    <t>(462/1248)</t>
+  </si>
+  <si>
+    <t>(2221/5635)</t>
+  </si>
+  <si>
+    <t>(792/2153)</t>
+  </si>
+  <si>
+    <t>(3273/4663)</t>
+  </si>
+  <si>
+    <t>(1558/2685)</t>
+  </si>
+  <si>
+    <t>(230/258)</t>
+  </si>
+  <si>
+    <t>(943/1097)</t>
+  </si>
+  <si>
+    <t>(494/737)</t>
+  </si>
+  <si>
+    <t>Testlauf 35 - 2026-10-07 10:55:52</t>
+  </si>
+  <si>
+    <t>(1650/2862)</t>
+  </si>
+  <si>
+    <t>(6627/13005)</t>
+  </si>
+  <si>
+    <t>(3042/6472)</t>
+  </si>
+  <si>
+    <t>(2370/4663)</t>
+  </si>
+  <si>
+    <t>(1237/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 36 - 2026-10-07 11:11:09</t>
+  </si>
+  <si>
+    <t>(6624/13005)</t>
+  </si>
+  <si>
+    <t>(3041/6472)</t>
+  </si>
+  <si>
+    <t>(2367/4663)</t>
+  </si>
+  <si>
+    <t>Testlauf 37 - 2026-10-07 13:07:35</t>
+  </si>
+  <si>
+    <t>(1876/2862)</t>
+  </si>
+  <si>
+    <t>(7711/13005)</t>
+  </si>
+  <si>
+    <t>(3419/6472)</t>
+  </si>
+  <si>
+    <t>(796/2153)</t>
+  </si>
+  <si>
+    <t>(3301/4663)</t>
+  </si>
+  <si>
+    <t>(1567/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 38 - 2026-10-07 13:12:39</t>
+  </si>
+  <si>
+    <t>(1859/2862)</t>
+  </si>
+  <si>
+    <t>(7640/13005)</t>
+  </si>
+  <si>
+    <t>(3379/6472)</t>
+  </si>
+  <si>
+    <t>(795/2153)</t>
+  </si>
+  <si>
+    <t>(3275/4663)</t>
+  </si>
+  <si>
+    <t>(1556/2685)</t>
   </si>
 </sst>
 </file>
@@ -870,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J436"/>
+  <dimension ref="A1:J670"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -10540,6 +10864,5193 @@
         <v>244</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="0" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C441" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E441" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G441" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I441" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C442" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D442" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E442" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="F442" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="G442" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H442" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="I442" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J442" s="0" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C443" s="0">
+        <v>1</v>
+      </c>
+      <c r="D443" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E443" s="0">
+        <v>1</v>
+      </c>
+      <c r="F443" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G443" s="0">
+        <v>1</v>
+      </c>
+      <c r="H443" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I443" s="0">
+        <v>1</v>
+      </c>
+      <c r="J443" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C444" s="0">
+        <v>1</v>
+      </c>
+      <c r="D444" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E444" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F444" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G444" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H444" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I444" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J444" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C445" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D445" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E445" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F445" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G445" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H445" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="I445" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J445" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C446" s="0">
+        <v>1</v>
+      </c>
+      <c r="D446" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E446" s="0">
+        <v>1</v>
+      </c>
+      <c r="F446" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G446" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H446" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I446" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J446" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C447" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D447" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E447" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F447" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="G447" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H447" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="I447" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J447" s="0" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C448" s="0">
+        <v>1</v>
+      </c>
+      <c r="D448" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E448" s="0">
+        <v>1</v>
+      </c>
+      <c r="F448" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G448" s="0">
+        <v>1</v>
+      </c>
+      <c r="H448" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I448" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J448" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C449" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D449" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E449" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F449" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G449" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H449" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I449" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J449" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C450" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D450" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E450" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F450" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G450" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H450" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I450" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J450" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C451" s="0">
+        <v>1</v>
+      </c>
+      <c r="D451" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E451" s="0">
+        <v>1</v>
+      </c>
+      <c r="F451" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G451" s="0">
+        <v>1</v>
+      </c>
+      <c r="H451" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I451" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J451" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C452" s="0">
+        <v>0</v>
+      </c>
+      <c r="D452" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E452" s="0">
+        <v>0</v>
+      </c>
+      <c r="F452" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G452" s="0">
+        <v>0</v>
+      </c>
+      <c r="H452" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I452" s="0">
+        <v>0</v>
+      </c>
+      <c r="J452" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C453" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D453" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E453" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F453" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G453" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H453" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I453" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J453" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C454" s="0">
+        <v>1</v>
+      </c>
+      <c r="D454" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E454" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F454" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G454" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H454" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I454" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J454" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C459" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E459" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G459" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I459" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C460" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D460" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E460" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F460" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="G460" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H460" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="I460" s="0">
+        <v>0.52</v>
+      </c>
+      <c r="J460" s="0" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C461" s="0">
+        <v>1</v>
+      </c>
+      <c r="D461" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E461" s="0">
+        <v>1</v>
+      </c>
+      <c r="F461" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G461" s="0">
+        <v>1</v>
+      </c>
+      <c r="H461" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I461" s="0">
+        <v>1</v>
+      </c>
+      <c r="J461" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C462" s="0">
+        <v>1</v>
+      </c>
+      <c r="D462" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E462" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F462" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G462" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H462" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I462" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J462" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C463" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D463" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E463" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F463" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G463" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H463" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="I463" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J463" s="0" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C464" s="0">
+        <v>1</v>
+      </c>
+      <c r="D464" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E464" s="0">
+        <v>1</v>
+      </c>
+      <c r="F464" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G464" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H464" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I464" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J464" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C465" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D465" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E465" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F465" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="G465" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H465" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="I465" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J465" s="0" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C466" s="0">
+        <v>1</v>
+      </c>
+      <c r="D466" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E466" s="0">
+        <v>1</v>
+      </c>
+      <c r="F466" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G466" s="0">
+        <v>1</v>
+      </c>
+      <c r="H466" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I466" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J466" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C467" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D467" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E467" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F467" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G467" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="H467" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="I467" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J467" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C468" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D468" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E468" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F468" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G468" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H468" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I468" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J468" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C469" s="0">
+        <v>1</v>
+      </c>
+      <c r="D469" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E469" s="0">
+        <v>1</v>
+      </c>
+      <c r="F469" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G469" s="0">
+        <v>1</v>
+      </c>
+      <c r="H469" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I469" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J469" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C470" s="0">
+        <v>1</v>
+      </c>
+      <c r="D470" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E470" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F470" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G470" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H470" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I470" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J470" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C471" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D471" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E471" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F471" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G471" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H471" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I471" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J471" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C472" s="0">
+        <v>1</v>
+      </c>
+      <c r="D472" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E472" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F472" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G472" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H472" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I472" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J472" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C477" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E477" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G477" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I477" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C478" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="D478" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="E478" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="F478" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="G478" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H478" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="I478" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J478" s="0" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C479" s="0">
+        <v>1</v>
+      </c>
+      <c r="D479" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E479" s="0">
+        <v>1</v>
+      </c>
+      <c r="F479" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G479" s="0">
+        <v>1</v>
+      </c>
+      <c r="H479" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I479" s="0">
+        <v>1</v>
+      </c>
+      <c r="J479" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C480" s="0">
+        <v>1</v>
+      </c>
+      <c r="D480" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E480" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F480" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G480" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H480" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I480" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J480" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C481" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="D481" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="E481" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F481" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="G481" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H481" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="I481" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J481" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C482" s="0">
+        <v>1</v>
+      </c>
+      <c r="D482" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E482" s="0">
+        <v>1</v>
+      </c>
+      <c r="F482" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G482" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H482" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I482" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J482" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C483" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D483" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E483" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F483" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="G483" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H483" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="I483" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J483" s="0" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C484" s="0">
+        <v>1</v>
+      </c>
+      <c r="D484" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E484" s="0">
+        <v>1</v>
+      </c>
+      <c r="F484" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G484" s="0">
+        <v>1</v>
+      </c>
+      <c r="H484" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I484" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J484" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C485" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D485" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E485" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F485" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G485" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H485" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I485" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J485" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C486" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D486" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E486" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F486" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G486" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H486" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I486" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J486" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C487" s="0">
+        <v>1</v>
+      </c>
+      <c r="D487" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E487" s="0">
+        <v>1</v>
+      </c>
+      <c r="F487" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G487" s="0">
+        <v>1</v>
+      </c>
+      <c r="H487" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I487" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J487" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C488" s="0">
+        <v>0</v>
+      </c>
+      <c r="D488" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E488" s="0">
+        <v>0</v>
+      </c>
+      <c r="F488" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G488" s="0">
+        <v>0</v>
+      </c>
+      <c r="H488" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I488" s="0">
+        <v>0</v>
+      </c>
+      <c r="J488" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C489" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D489" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E489" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F489" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G489" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H489" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I489" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J489" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C490" s="0">
+        <v>1</v>
+      </c>
+      <c r="D490" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E490" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F490" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G490" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H490" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I490" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J490" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="0" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C495" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E495" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G495" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I495" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C496" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D496" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E496" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="F496" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G496" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H496" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="I496" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J496" s="0" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C497" s="0">
+        <v>1</v>
+      </c>
+      <c r="D497" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E497" s="0">
+        <v>1</v>
+      </c>
+      <c r="F497" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G497" s="0">
+        <v>1</v>
+      </c>
+      <c r="H497" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I497" s="0">
+        <v>1</v>
+      </c>
+      <c r="J497" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C498" s="0">
+        <v>1</v>
+      </c>
+      <c r="D498" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E498" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F498" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G498" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H498" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I498" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J498" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C499" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D499" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E499" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="F499" s="0" t="s">
+        <v>315</v>
+      </c>
+      <c r="G499" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H499" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="I499" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J499" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C500" s="0">
+        <v>1</v>
+      </c>
+      <c r="D500" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E500" s="0">
+        <v>1</v>
+      </c>
+      <c r="F500" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G500" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H500" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I500" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J500" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C501" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D501" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E501" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F501" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="G501" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H501" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="I501" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J501" s="0" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C502" s="0">
+        <v>1</v>
+      </c>
+      <c r="D502" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E502" s="0">
+        <v>1</v>
+      </c>
+      <c r="F502" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G502" s="0">
+        <v>1</v>
+      </c>
+      <c r="H502" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I502" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J502" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C503" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D503" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E503" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F503" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G503" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="H503" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="I503" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J503" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C504" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D504" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E504" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F504" s="0" t="s">
+        <v>317</v>
+      </c>
+      <c r="G504" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H504" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="I504" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J504" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C505" s="0">
+        <v>1</v>
+      </c>
+      <c r="D505" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E505" s="0">
+        <v>1</v>
+      </c>
+      <c r="F505" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G505" s="0">
+        <v>1</v>
+      </c>
+      <c r="H505" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I505" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J505" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C506" s="0">
+        <v>0</v>
+      </c>
+      <c r="D506" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E506" s="0">
+        <v>0</v>
+      </c>
+      <c r="F506" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G506" s="0">
+        <v>0</v>
+      </c>
+      <c r="H506" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I506" s="0">
+        <v>0</v>
+      </c>
+      <c r="J506" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C507" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D507" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E507" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F507" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G507" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H507" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I507" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J507" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C508" s="0">
+        <v>1</v>
+      </c>
+      <c r="D508" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E508" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F508" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G508" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H508" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I508" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J508" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C513" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E513" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G513" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I513" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C514" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D514" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E514" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="F514" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="G514" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H514" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="I514" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J514" s="0" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C515" s="0">
+        <v>1</v>
+      </c>
+      <c r="D515" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E515" s="0">
+        <v>1</v>
+      </c>
+      <c r="F515" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G515" s="0">
+        <v>1</v>
+      </c>
+      <c r="H515" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I515" s="0">
+        <v>1</v>
+      </c>
+      <c r="J515" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C516" s="0">
+        <v>1</v>
+      </c>
+      <c r="D516" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E516" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F516" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G516" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H516" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I516" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J516" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C517" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D517" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E517" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F517" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="G517" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H517" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="I517" s="0">
+        <v>0.36</v>
+      </c>
+      <c r="J517" s="0" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C518" s="0">
+        <v>1</v>
+      </c>
+      <c r="D518" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E518" s="0">
+        <v>1</v>
+      </c>
+      <c r="F518" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G518" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H518" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I518" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J518" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C519" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D519" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E519" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F519" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="G519" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H519" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="I519" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J519" s="0" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C520" s="0">
+        <v>1</v>
+      </c>
+      <c r="D520" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E520" s="0">
+        <v>1</v>
+      </c>
+      <c r="F520" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G520" s="0">
+        <v>1</v>
+      </c>
+      <c r="H520" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I520" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J520" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C521" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D521" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E521" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F521" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G521" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H521" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I521" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J521" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C522" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D522" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E522" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F522" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G522" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H522" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I522" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J522" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C523" s="0">
+        <v>1</v>
+      </c>
+      <c r="D523" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E523" s="0">
+        <v>1</v>
+      </c>
+      <c r="F523" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G523" s="0">
+        <v>1</v>
+      </c>
+      <c r="H523" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I523" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J523" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C524" s="0">
+        <v>0</v>
+      </c>
+      <c r="D524" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E524" s="0">
+        <v>0</v>
+      </c>
+      <c r="F524" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G524" s="0">
+        <v>0</v>
+      </c>
+      <c r="H524" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I524" s="0">
+        <v>0</v>
+      </c>
+      <c r="J524" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C525" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D525" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E525" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F525" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G525" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H525" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I525" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J525" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C526" s="0">
+        <v>1</v>
+      </c>
+      <c r="D526" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E526" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F526" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G526" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H526" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I526" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J526" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="0" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C531" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E531" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G531" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I531" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C532" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D532" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E532" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F532" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="G532" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H532" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="I532" s="0">
+        <v>0.52</v>
+      </c>
+      <c r="J532" s="0" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C533" s="0">
+        <v>1</v>
+      </c>
+      <c r="D533" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E533" s="0">
+        <v>1</v>
+      </c>
+      <c r="F533" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G533" s="0">
+        <v>1</v>
+      </c>
+      <c r="H533" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I533" s="0">
+        <v>1</v>
+      </c>
+      <c r="J533" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C534" s="0">
+        <v>1</v>
+      </c>
+      <c r="D534" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E534" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F534" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G534" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H534" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I534" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J534" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C535" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D535" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E535" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F535" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G535" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H535" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="I535" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J535" s="0" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C536" s="0">
+        <v>1</v>
+      </c>
+      <c r="D536" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E536" s="0">
+        <v>1</v>
+      </c>
+      <c r="F536" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G536" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H536" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I536" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J536" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C537" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D537" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E537" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F537" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="G537" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H537" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="I537" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J537" s="0" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C538" s="0">
+        <v>1</v>
+      </c>
+      <c r="D538" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E538" s="0">
+        <v>1</v>
+      </c>
+      <c r="F538" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G538" s="0">
+        <v>1</v>
+      </c>
+      <c r="H538" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I538" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J538" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C539" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D539" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E539" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F539" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G539" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H539" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I539" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J539" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C540" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D540" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E540" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F540" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G540" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H540" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="I540" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J540" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C541" s="0">
+        <v>1</v>
+      </c>
+      <c r="D541" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E541" s="0">
+        <v>1</v>
+      </c>
+      <c r="F541" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G541" s="0">
+        <v>1</v>
+      </c>
+      <c r="H541" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I541" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J541" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C542" s="0">
+        <v>1</v>
+      </c>
+      <c r="D542" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E542" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F542" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G542" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H542" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I542" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J542" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C543" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D543" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E543" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F543" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G543" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H543" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I543" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J543" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C544" s="0">
+        <v>1</v>
+      </c>
+      <c r="D544" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E544" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F544" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G544" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H544" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I544" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J544" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="0" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C549" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E549" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G549" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I549" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C550" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D550" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="E550" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="F550" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="G550" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H550" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="I550" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J550" s="0" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C551" s="0">
+        <v>1</v>
+      </c>
+      <c r="D551" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E551" s="0">
+        <v>1</v>
+      </c>
+      <c r="F551" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G551" s="0">
+        <v>1</v>
+      </c>
+      <c r="H551" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I551" s="0">
+        <v>1</v>
+      </c>
+      <c r="J551" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C552" s="0">
+        <v>1</v>
+      </c>
+      <c r="D552" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E552" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F552" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G552" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H552" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I552" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J552" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C553" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D553" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E553" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F553" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="G553" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H553" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="I553" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J553" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C554" s="0">
+        <v>1</v>
+      </c>
+      <c r="D554" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E554" s="0">
+        <v>1</v>
+      </c>
+      <c r="F554" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G554" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H554" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I554" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J554" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C555" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D555" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="E555" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F555" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="G555" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="H555" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="I555" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J555" s="0" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C556" s="0">
+        <v>1</v>
+      </c>
+      <c r="D556" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E556" s="0">
+        <v>1</v>
+      </c>
+      <c r="F556" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G556" s="0">
+        <v>1</v>
+      </c>
+      <c r="H556" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I556" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J556" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C557" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D557" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E557" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F557" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G557" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="H557" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="I557" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J557" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C558" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D558" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E558" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F558" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G558" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H558" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I558" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J558" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C559" s="0">
+        <v>1</v>
+      </c>
+      <c r="D559" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E559" s="0">
+        <v>1</v>
+      </c>
+      <c r="F559" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G559" s="0">
+        <v>1</v>
+      </c>
+      <c r="H559" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I559" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J559" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C560" s="0">
+        <v>0</v>
+      </c>
+      <c r="D560" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E560" s="0">
+        <v>0</v>
+      </c>
+      <c r="F560" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G560" s="0">
+        <v>0</v>
+      </c>
+      <c r="H560" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I560" s="0">
+        <v>0</v>
+      </c>
+      <c r="J560" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C561" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D561" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E561" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F561" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G561" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H561" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I561" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J561" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C562" s="0">
+        <v>1</v>
+      </c>
+      <c r="D562" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E562" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F562" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G562" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H562" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I562" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J562" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="0" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C567" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E567" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G567" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I567" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C568" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D568" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E568" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="F568" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="G568" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H568" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="I568" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J568" s="0" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C569" s="0">
+        <v>1</v>
+      </c>
+      <c r="D569" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E569" s="0">
+        <v>1</v>
+      </c>
+      <c r="F569" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G569" s="0">
+        <v>1</v>
+      </c>
+      <c r="H569" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I569" s="0">
+        <v>1</v>
+      </c>
+      <c r="J569" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C570" s="0">
+        <v>1</v>
+      </c>
+      <c r="D570" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E570" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F570" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G570" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H570" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I570" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J570" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C571" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D571" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E571" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F571" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="G571" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H571" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="I571" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J571" s="0" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C572" s="0">
+        <v>1</v>
+      </c>
+      <c r="D572" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E572" s="0">
+        <v>1</v>
+      </c>
+      <c r="F572" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G572" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H572" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I572" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J572" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C573" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D573" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E573" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F573" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="G573" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H573" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="I573" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J573" s="0" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C574" s="0">
+        <v>1</v>
+      </c>
+      <c r="D574" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E574" s="0">
+        <v>1</v>
+      </c>
+      <c r="F574" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G574" s="0">
+        <v>1</v>
+      </c>
+      <c r="H574" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I574" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J574" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C575" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D575" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E575" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F575" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G575" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="H575" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="I575" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J575" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C576" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D576" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E576" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F576" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G576" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H576" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I576" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J576" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C577" s="0">
+        <v>1</v>
+      </c>
+      <c r="D577" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E577" s="0">
+        <v>1</v>
+      </c>
+      <c r="F577" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G577" s="0">
+        <v>1</v>
+      </c>
+      <c r="H577" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I577" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J577" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C578" s="0">
+        <v>0</v>
+      </c>
+      <c r="D578" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E578" s="0">
+        <v>0</v>
+      </c>
+      <c r="F578" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G578" s="0">
+        <v>0</v>
+      </c>
+      <c r="H578" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I578" s="0">
+        <v>0</v>
+      </c>
+      <c r="J578" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C579" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D579" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E579" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F579" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G579" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H579" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I579" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J579" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C580" s="0">
+        <v>1</v>
+      </c>
+      <c r="D580" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E580" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F580" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G580" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H580" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I580" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J580" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="0" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C585" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E585" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G585" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I585" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C586" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D586" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E586" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F586" s="0" t="s">
+        <v>344</v>
+      </c>
+      <c r="G586" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H586" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="I586" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J586" s="0" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C587" s="0">
+        <v>1</v>
+      </c>
+      <c r="D587" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E587" s="0">
+        <v>1</v>
+      </c>
+      <c r="F587" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G587" s="0">
+        <v>1</v>
+      </c>
+      <c r="H587" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I587" s="0">
+        <v>1</v>
+      </c>
+      <c r="J587" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C588" s="0">
+        <v>1</v>
+      </c>
+      <c r="D588" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E588" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F588" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G588" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H588" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I588" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J588" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C589" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D589" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E589" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F589" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="G589" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H589" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="I589" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J589" s="0" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C590" s="0">
+        <v>1</v>
+      </c>
+      <c r="D590" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E590" s="0">
+        <v>1</v>
+      </c>
+      <c r="F590" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G590" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H590" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I590" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J590" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C591" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D591" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E591" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F591" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="G591" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H591" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="I591" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J591" s="0" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C592" s="0">
+        <v>1</v>
+      </c>
+      <c r="D592" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E592" s="0">
+        <v>1</v>
+      </c>
+      <c r="F592" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G592" s="0">
+        <v>1</v>
+      </c>
+      <c r="H592" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I592" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J592" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C593" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D593" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E593" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F593" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G593" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H593" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I593" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J593" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C594" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D594" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E594" s="0">
+        <v>0.89</v>
+      </c>
+      <c r="F594" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="G594" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="H594" s="0" t="s">
+        <v>353</v>
+      </c>
+      <c r="I594" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J594" s="0" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C595" s="0">
+        <v>1</v>
+      </c>
+      <c r="D595" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E595" s="0">
+        <v>1</v>
+      </c>
+      <c r="F595" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G595" s="0">
+        <v>1</v>
+      </c>
+      <c r="H595" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I595" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J595" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C596" s="0">
+        <v>1</v>
+      </c>
+      <c r="D596" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E596" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F596" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G596" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H596" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I596" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J596" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C597" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D597" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E597" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F597" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G597" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H597" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I597" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J597" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C598" s="0">
+        <v>1</v>
+      </c>
+      <c r="D598" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E598" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F598" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G598" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H598" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I598" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J598" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="0" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C603" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E603" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G603" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I603" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C604" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D604" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E604" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="F604" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G604" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H604" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="I604" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J604" s="0" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C605" s="0">
+        <v>1</v>
+      </c>
+      <c r="D605" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E605" s="0">
+        <v>1</v>
+      </c>
+      <c r="F605" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G605" s="0">
+        <v>1</v>
+      </c>
+      <c r="H605" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I605" s="0">
+        <v>1</v>
+      </c>
+      <c r="J605" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C606" s="0">
+        <v>1</v>
+      </c>
+      <c r="D606" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E606" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F606" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G606" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H606" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I606" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J606" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C607" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D607" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E607" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F607" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="G607" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H607" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="I607" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J607" s="0" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C608" s="0">
+        <v>1</v>
+      </c>
+      <c r="D608" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E608" s="0">
+        <v>1</v>
+      </c>
+      <c r="F608" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G608" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H608" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I608" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J608" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C609" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D609" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E609" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F609" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="G609" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H609" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="I609" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J609" s="0" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C610" s="0">
+        <v>1</v>
+      </c>
+      <c r="D610" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E610" s="0">
+        <v>1</v>
+      </c>
+      <c r="F610" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G610" s="0">
+        <v>1</v>
+      </c>
+      <c r="H610" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I610" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J610" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C611" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D611" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E611" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F611" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G611" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H611" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I611" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J611" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C612" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D612" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E612" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F612" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G612" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H612" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I612" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J612" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C613" s="0">
+        <v>1</v>
+      </c>
+      <c r="D613" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E613" s="0">
+        <v>1</v>
+      </c>
+      <c r="F613" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G613" s="0">
+        <v>1</v>
+      </c>
+      <c r="H613" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I613" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J613" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C614" s="0">
+        <v>0</v>
+      </c>
+      <c r="D614" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E614" s="0">
+        <v>0</v>
+      </c>
+      <c r="F614" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G614" s="0">
+        <v>0</v>
+      </c>
+      <c r="H614" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I614" s="0">
+        <v>0</v>
+      </c>
+      <c r="J614" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C615" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D615" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E615" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F615" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G615" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H615" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I615" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J615" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C616" s="0">
+        <v>1</v>
+      </c>
+      <c r="D616" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E616" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F616" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G616" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H616" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I616" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J616" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="0" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C621" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E621" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G621" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I621" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C622" s="0">
+        <v>0.74</v>
+      </c>
+      <c r="D622" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="E622" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="F622" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="G622" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H622" s="0" t="s">
+        <v>362</v>
+      </c>
+      <c r="I622" s="0">
+        <v>0.47</v>
+      </c>
+      <c r="J622" s="0" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C623" s="0">
+        <v>1</v>
+      </c>
+      <c r="D623" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E623" s="0">
+        <v>1</v>
+      </c>
+      <c r="F623" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G623" s="0">
+        <v>1</v>
+      </c>
+      <c r="H623" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I623" s="0">
+        <v>1</v>
+      </c>
+      <c r="J623" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C624" s="0">
+        <v>1</v>
+      </c>
+      <c r="D624" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E624" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F624" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G624" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H624" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I624" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J624" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C625" s="0">
+        <v>0.62</v>
+      </c>
+      <c r="D625" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="E625" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F625" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="G625" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H625" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="I625" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J625" s="0" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C626" s="0">
+        <v>1</v>
+      </c>
+      <c r="D626" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E626" s="0">
+        <v>1</v>
+      </c>
+      <c r="F626" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G626" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H626" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I626" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J626" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C627" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="D627" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="E627" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F627" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="G627" s="0">
+        <v>0.51</v>
+      </c>
+      <c r="H627" s="0" t="s">
+        <v>364</v>
+      </c>
+      <c r="I627" s="0">
+        <v>0.46</v>
+      </c>
+      <c r="J627" s="0" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C628" s="0">
+        <v>1</v>
+      </c>
+      <c r="D628" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E628" s="0">
+        <v>1</v>
+      </c>
+      <c r="F628" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G628" s="0">
+        <v>1</v>
+      </c>
+      <c r="H628" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I628" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J628" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C629" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D629" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E629" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F629" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G629" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H629" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I629" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J629" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C630" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D630" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E630" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F630" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="G630" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H630" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="I630" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J630" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C631" s="0">
+        <v>1</v>
+      </c>
+      <c r="D631" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E631" s="0">
+        <v>1</v>
+      </c>
+      <c r="F631" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G631" s="0">
+        <v>1</v>
+      </c>
+      <c r="H631" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I631" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J631" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C632" s="0">
+        <v>0</v>
+      </c>
+      <c r="D632" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="E632" s="0">
+        <v>0</v>
+      </c>
+      <c r="F632" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="G632" s="0">
+        <v>0</v>
+      </c>
+      <c r="H632" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="I632" s="0">
+        <v>0</v>
+      </c>
+      <c r="J632" s="0" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C633" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D633" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E633" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="F633" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="G633" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H633" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="I633" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J633" s="0" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C634" s="0">
+        <v>1</v>
+      </c>
+      <c r="D634" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E634" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F634" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G634" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H634" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I634" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J634" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="0" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C639" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E639" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G639" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I639" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C640" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D640" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E640" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="F640" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="G640" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H640" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="I640" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J640" s="0" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C641" s="0">
+        <v>1</v>
+      </c>
+      <c r="D641" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E641" s="0">
+        <v>1</v>
+      </c>
+      <c r="F641" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G641" s="0">
+        <v>1</v>
+      </c>
+      <c r="H641" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I641" s="0">
+        <v>1</v>
+      </c>
+      <c r="J641" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C642" s="0">
+        <v>1</v>
+      </c>
+      <c r="D642" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E642" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F642" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G642" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H642" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I642" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J642" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C643" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D643" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E643" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F643" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="G643" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H643" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I643" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J643" s="0" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C644" s="0">
+        <v>1</v>
+      </c>
+      <c r="D644" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E644" s="0">
+        <v>1</v>
+      </c>
+      <c r="F644" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G644" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H644" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I644" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J644" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C645" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D645" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E645" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F645" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="G645" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H645" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="I645" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J645" s="0" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C646" s="0">
+        <v>1</v>
+      </c>
+      <c r="D646" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E646" s="0">
+        <v>1</v>
+      </c>
+      <c r="F646" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G646" s="0">
+        <v>1</v>
+      </c>
+      <c r="H646" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I646" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J646" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C647" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D647" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E647" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F647" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G647" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H647" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I647" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J647" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C648" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D648" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E648" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F648" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G648" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H648" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I648" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J648" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C649" s="0">
+        <v>1</v>
+      </c>
+      <c r="D649" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E649" s="0">
+        <v>1</v>
+      </c>
+      <c r="F649" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G649" s="0">
+        <v>1</v>
+      </c>
+      <c r="H649" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I649" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J649" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C650" s="0">
+        <v>1</v>
+      </c>
+      <c r="D650" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E650" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F650" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G650" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H650" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I650" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J650" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C651" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D651" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E651" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F651" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G651" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H651" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I651" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J651" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C652" s="0">
+        <v>1</v>
+      </c>
+      <c r="D652" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E652" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F652" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G652" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H652" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I652" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J652" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="0" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C657" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E657" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G657" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I657" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C658" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D658" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E658" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F658" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="G658" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H658" s="0" t="s">
+        <v>374</v>
+      </c>
+      <c r="I658" s="0">
+        <v>0.52</v>
+      </c>
+      <c r="J658" s="0" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C659" s="0">
+        <v>1</v>
+      </c>
+      <c r="D659" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E659" s="0">
+        <v>1</v>
+      </c>
+      <c r="F659" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G659" s="0">
+        <v>1</v>
+      </c>
+      <c r="H659" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I659" s="0">
+        <v>1</v>
+      </c>
+      <c r="J659" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C660" s="0">
+        <v>1</v>
+      </c>
+      <c r="D660" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E660" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F660" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G660" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H660" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I660" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J660" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C661" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D661" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E661" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F661" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="G661" s="0">
+        <v>0.4</v>
+      </c>
+      <c r="H661" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I661" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J661" s="0" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C662" s="0">
+        <v>1</v>
+      </c>
+      <c r="D662" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E662" s="0">
+        <v>1</v>
+      </c>
+      <c r="F662" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G662" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H662" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I662" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J662" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C663" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D663" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E663" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F663" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="G663" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H663" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="I663" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J663" s="0" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C664" s="0">
+        <v>1</v>
+      </c>
+      <c r="D664" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E664" s="0">
+        <v>1</v>
+      </c>
+      <c r="F664" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G664" s="0">
+        <v>1</v>
+      </c>
+      <c r="H664" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I664" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J664" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C665" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D665" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E665" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F665" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G665" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="H665" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="I665" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J665" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C666" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D666" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E666" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F666" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G666" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H666" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I666" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J666" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C667" s="0">
+        <v>1</v>
+      </c>
+      <c r="D667" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E667" s="0">
+        <v>1</v>
+      </c>
+      <c r="F667" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G667" s="0">
+        <v>1</v>
+      </c>
+      <c r="H667" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I667" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J667" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C668" s="0">
+        <v>1</v>
+      </c>
+      <c r="D668" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E668" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F668" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G668" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H668" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I668" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J668" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C669" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D669" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E669" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F669" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G669" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H669" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I669" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J669" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C670" s="0">
+        <v>1</v>
+      </c>
+      <c r="D670" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E670" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F670" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G670" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H670" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I670" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J670" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="386">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -1149,6 +1149,27 @@
   </si>
   <si>
     <t>(1556/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 39 - 2026-10-07 15:16:12</t>
+  </si>
+  <si>
+    <t>(1869/2862)</t>
+  </si>
+  <si>
+    <t>(7670/13005)</t>
+  </si>
+  <si>
+    <t>(3400/6472)</t>
+  </si>
+  <si>
+    <t>(797/928)</t>
+  </si>
+  <si>
+    <t>(3266/4663)</t>
+  </si>
+  <si>
+    <t>(1555/2685)</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J670"/>
+  <dimension ref="A1:J688"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -16051,6 +16072,405 @@
         <v>244</v>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C675" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E675" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G675" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I675" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C676" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D676" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E676" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F676" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="G676" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H676" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="I676" s="0">
+        <v>0.53</v>
+      </c>
+      <c r="J676" s="0" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C677" s="0">
+        <v>1</v>
+      </c>
+      <c r="D677" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E677" s="0">
+        <v>1</v>
+      </c>
+      <c r="F677" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G677" s="0">
+        <v>1</v>
+      </c>
+      <c r="H677" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I677" s="0">
+        <v>1</v>
+      </c>
+      <c r="J677" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C678" s="0">
+        <v>1</v>
+      </c>
+      <c r="D678" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E678" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F678" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G678" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H678" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I678" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J678" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C679" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D679" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E679" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F679" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="G679" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H679" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="I679" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J679" s="0" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C680" s="0">
+        <v>1</v>
+      </c>
+      <c r="D680" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E680" s="0">
+        <v>1</v>
+      </c>
+      <c r="F680" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G680" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H680" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I680" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J680" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C681" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D681" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E681" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F681" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="G681" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H681" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="I681" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J681" s="0" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C682" s="0">
+        <v>1</v>
+      </c>
+      <c r="D682" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E682" s="0">
+        <v>1</v>
+      </c>
+      <c r="F682" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G682" s="0">
+        <v>1</v>
+      </c>
+      <c r="H682" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I682" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J682" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C683" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D683" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E683" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F683" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G683" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H683" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I683" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="J683" s="0" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C684" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D684" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E684" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F684" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G684" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H684" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I684" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J684" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C685" s="0">
+        <v>1</v>
+      </c>
+      <c r="D685" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E685" s="0">
+        <v>1</v>
+      </c>
+      <c r="F685" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G685" s="0">
+        <v>1</v>
+      </c>
+      <c r="H685" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I685" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J685" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C686" s="0">
+        <v>1</v>
+      </c>
+      <c r="D686" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E686" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F686" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G686" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H686" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I686" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J686" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C687" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D687" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E687" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F687" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G687" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H687" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I687" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J687" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C688" s="0">
+        <v>1</v>
+      </c>
+      <c r="D688" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E688" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F688" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G688" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H688" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I688" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J688" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="395">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -1170,6 +1170,33 @@
   </si>
   <si>
     <t>(1555/2685)</t>
+  </si>
+  <si>
+    <t>Testlauf 40 - 2026-10-09 15:10:47</t>
+  </si>
+  <si>
+    <t>(7668/13005)</t>
+  </si>
+  <si>
+    <t>(3397/6472)</t>
+  </si>
+  <si>
+    <t>(2223/5635)</t>
+  </si>
+  <si>
+    <t>(794/2153)</t>
+  </si>
+  <si>
+    <t>(798/928)</t>
+  </si>
+  <si>
+    <t>(3262/4663)</t>
+  </si>
+  <si>
+    <t>(1546/2685)</t>
+  </si>
+  <si>
+    <t>(473/737)</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J688"/>
+  <dimension ref="A1:J706"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -16471,6 +16498,405 @@
         <v>244</v>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" s="0" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C693" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E693" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G693" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I693" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C694" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D694" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E694" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F694" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="G694" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H694" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="I694" s="0">
+        <v>0.52</v>
+      </c>
+      <c r="J694" s="0" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C695" s="0">
+        <v>1</v>
+      </c>
+      <c r="D695" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E695" s="0">
+        <v>1</v>
+      </c>
+      <c r="F695" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G695" s="0">
+        <v>1</v>
+      </c>
+      <c r="H695" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I695" s="0">
+        <v>1</v>
+      </c>
+      <c r="J695" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C696" s="0">
+        <v>1</v>
+      </c>
+      <c r="D696" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E696" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F696" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G696" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H696" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I696" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J696" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C697" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D697" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E697" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F697" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G697" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H697" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="I697" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J697" s="0" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C698" s="0">
+        <v>1</v>
+      </c>
+      <c r="D698" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E698" s="0">
+        <v>1</v>
+      </c>
+      <c r="F698" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G698" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H698" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I698" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J698" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C699" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D699" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E699" s="0">
+        <v>0.86</v>
+      </c>
+      <c r="F699" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="G699" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="H699" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="I699" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J699" s="0" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C700" s="0">
+        <v>1</v>
+      </c>
+      <c r="D700" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E700" s="0">
+        <v>1</v>
+      </c>
+      <c r="F700" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G700" s="0">
+        <v>1</v>
+      </c>
+      <c r="H700" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I700" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J700" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C701" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D701" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E701" s="0">
+        <v>0.81</v>
+      </c>
+      <c r="F701" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="G701" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="H701" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="I701" s="0">
+        <v>0.67</v>
+      </c>
+      <c r="J701" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C702" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D702" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E702" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F702" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G702" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H702" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I702" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J702" s="0" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C703" s="0">
+        <v>1</v>
+      </c>
+      <c r="D703" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E703" s="0">
+        <v>1</v>
+      </c>
+      <c r="F703" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G703" s="0">
+        <v>1</v>
+      </c>
+      <c r="H703" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I703" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J703" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C704" s="0">
+        <v>1</v>
+      </c>
+      <c r="D704" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E704" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F704" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G704" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H704" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I704" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J704" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C705" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D705" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E705" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F705" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G705" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H705" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I705" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J705" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C706" s="0">
+        <v>1</v>
+      </c>
+      <c r="D706" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E706" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F706" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G706" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H706" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I706" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J706" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/test_coverage_history.xlsx
+++ b/test_coverage_history.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
   <si>
     <t>Testlauf 1 - 2026-09-18 21:17:25</t>
   </si>
@@ -1197,6 +1197,24 @@
   </si>
   <si>
     <t>(473/737)</t>
+  </si>
+  <si>
+    <t>Testlauf 41 - 2026-10-09 16:33:06</t>
+  </si>
+  <si>
+    <t>(7689/13005)</t>
+  </si>
+  <si>
+    <t>(3389/6472)</t>
+  </si>
+  <si>
+    <t>(793/2153)</t>
+  </si>
+  <si>
+    <t>(810/928)</t>
+  </si>
+  <si>
+    <t>(3328/4663)</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J706"/>
+  <dimension ref="A1:J724"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.0140705108643" customWidth="1"/>
@@ -16897,6 +16915,405 @@
         <v>244</v>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" s="0" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C711" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E711" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G711" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="I711" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C712" s="0">
+        <v>0.82</v>
+      </c>
+      <c r="D712" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="E712" s="0">
+        <v>0.65</v>
+      </c>
+      <c r="F712" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="G712" s="0">
+        <v>0.59</v>
+      </c>
+      <c r="H712" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="I712" s="0">
+        <v>0.52</v>
+      </c>
+      <c r="J712" s="0" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C713" s="0">
+        <v>1</v>
+      </c>
+      <c r="D713" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E713" s="0">
+        <v>1</v>
+      </c>
+      <c r="F713" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="G713" s="0">
+        <v>1</v>
+      </c>
+      <c r="H713" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="I713" s="0">
+        <v>1</v>
+      </c>
+      <c r="J713" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C714" s="0">
+        <v>1</v>
+      </c>
+      <c r="D714" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E714" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="F714" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="G714" s="0">
+        <v>0.84</v>
+      </c>
+      <c r="H714" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="I714" s="0">
+        <v>0.77</v>
+      </c>
+      <c r="J714" s="0" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C715" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="D715" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="E715" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="F715" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="G715" s="0">
+        <v>0.39</v>
+      </c>
+      <c r="H715" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="I715" s="0">
+        <v>0.37</v>
+      </c>
+      <c r="J715" s="0" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C716" s="0">
+        <v>1</v>
+      </c>
+      <c r="D716" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E716" s="0">
+        <v>1</v>
+      </c>
+      <c r="F716" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="0">
+        <v>0.91</v>
+      </c>
+      <c r="H716" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I716" s="0">
+        <v>0.76</v>
+      </c>
+      <c r="J716" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C717" s="0">
+        <v>0.98</v>
+      </c>
+      <c r="D717" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="E717" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F717" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="G717" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="H717" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="I717" s="0">
+        <v>0.58</v>
+      </c>
+      <c r="J717" s="0" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C718" s="0">
+        <v>1</v>
+      </c>
+      <c r="D718" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E718" s="0">
+        <v>1</v>
+      </c>
+      <c r="F718" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G718" s="0">
+        <v>1</v>
+      </c>
+      <c r="H718" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I718" s="0">
+        <v>0.93</v>
+      </c>
+      <c r="J718" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C719" s="0">
+        <v>0.85</v>
+      </c>
+      <c r="D719" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="E719" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="F719" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G719" s="0">
+        <v>0.66</v>
+      </c>
+      <c r="H719" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="I719" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J719" s="0" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C720" s="0">
+        <v>0.97</v>
+      </c>
+      <c r="D720" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E720" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="F720" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G720" s="0">
+        <v>0.83</v>
+      </c>
+      <c r="H720" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="I720" s="0">
+        <v>0.64</v>
+      </c>
+      <c r="J720" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C721" s="0">
+        <v>1</v>
+      </c>
+      <c r="D721" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E721" s="0">
+        <v>1</v>
+      </c>
+      <c r="F721" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="G721" s="0">
+        <v>1</v>
+      </c>
+      <c r="H721" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="I721" s="0">
+        <v>0.71</v>
+      </c>
+      <c r="J721" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C722" s="0">
+        <v>1</v>
+      </c>
+      <c r="D722" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E722" s="0">
+        <v>0.9</v>
+      </c>
+      <c r="F722" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G722" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H722" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="I722" s="0">
+        <v>0.41</v>
+      </c>
+      <c r="J722" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C723" s="0">
+        <v>0.88</v>
+      </c>
+      <c r="D723" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="E723" s="0">
+        <v>0.87</v>
+      </c>
+      <c r="F723" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="G723" s="0">
+        <v>0.72</v>
+      </c>
+      <c r="H723" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="I723" s="0">
+        <v>0.57</v>
+      </c>
+      <c r="J723" s="0" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C724" s="0">
+        <v>1</v>
+      </c>
+      <c r="D724" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="E724" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="F724" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="G724" s="0">
+        <v>0.32</v>
+      </c>
+      <c r="H724" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="I724" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J724" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
